--- a/public/Key-Point.xlsx
+++ b/public/Key-Point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\barab\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmakh\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BCC028-EB94-4AC2-9DAE-F50652BE4BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F434C4C-580C-4E99-BD30-C273354C1DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DT and Line Maintenance" sheetId="3" r:id="rId1"/>
@@ -268,7 +268,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -387,51 +387,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -905,7 +864,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -916,7 +875,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -925,229 +884,211 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="5" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="4" fillId="6" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="4" fillId="6" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1431,82 +1372,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4844BC35-A34B-47F3-A96A-272E32A32E1D}">
   <dimension ref="A1:S54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.453125" style="62" customWidth="1"/>
-    <col min="2" max="2" width="10.1796875" style="62" customWidth="1"/>
-    <col min="3" max="3" width="11.08984375" style="62" customWidth="1"/>
-    <col min="4" max="7" width="8.7265625" style="62"/>
-    <col min="8" max="8" width="9" style="62" customWidth="1"/>
-    <col min="9" max="9" width="12.81640625" style="62" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" style="62" customWidth="1"/>
-    <col min="11" max="11" width="13.54296875" style="62" customWidth="1"/>
-    <col min="12" max="12" width="11.36328125" style="62" customWidth="1"/>
-    <col min="13" max="13" width="11" style="62" customWidth="1"/>
-    <col min="14" max="14" width="11.81640625" style="62" customWidth="1"/>
-    <col min="15" max="15" width="11.453125" style="62" customWidth="1"/>
-    <col min="16" max="16" width="14.6328125" style="62" customWidth="1"/>
-    <col min="17" max="17" width="12.453125" style="62" customWidth="1"/>
-    <col min="18" max="18" width="10.6328125" style="62" customWidth="1"/>
-    <col min="19" max="19" width="12.6328125" style="62" customWidth="1"/>
-    <col min="20" max="16384" width="8.7265625" style="62"/>
+    <col min="1" max="1" width="23.44140625" style="34" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" style="34" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="34" customWidth="1"/>
+    <col min="4" max="7" width="8.77734375" style="34"/>
+    <col min="8" max="8" width="9" style="34" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="34" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" style="34" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" style="34" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" style="34" customWidth="1"/>
+    <col min="13" max="13" width="11" style="34" customWidth="1"/>
+    <col min="14" max="14" width="11.77734375" style="34" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="34" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" style="34" customWidth="1"/>
+    <col min="17" max="17" width="12.44140625" style="34" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" style="34" customWidth="1"/>
+    <col min="19" max="19" width="12.6640625" style="34" customWidth="1"/>
+    <col min="20" max="16384" width="8.77734375" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:19" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-    </row>
-    <row r="2" spans="1:19" ht="21.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="46" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+    </row>
+    <row r="2" spans="1:19" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="61" t="s">
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-    </row>
-    <row r="3" spans="1:19" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="47"/>
-      <c r="B3" s="49"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+    </row>
+    <row r="3" spans="1:19" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="61"/>
+      <c r="B3" s="63"/>
       <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1559,14 +1500,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A4" s="42" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="52" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="9">
         <v>45962</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="16">
         <v>120</v>
       </c>
       <c r="D4" s="5">
@@ -1584,13 +1525,13 @@
       <c r="H4" s="6">
         <v>0</v>
       </c>
-      <c r="I4" s="63">
+      <c r="I4" s="35">
         <v>229</v>
       </c>
-      <c r="J4" s="16">
-        <v>0</v>
-      </c>
-      <c r="K4" s="17">
+      <c r="J4" s="15">
+        <v>0</v>
+      </c>
+      <c r="K4" s="16">
         <v>10</v>
       </c>
       <c r="L4" s="6">
@@ -1612,18 +1553,18 @@
         <v>5</v>
       </c>
       <c r="R4" s="6">
-        <v>78</v>
+        <v>178</v>
       </c>
       <c r="S4" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A5" s="42"/>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="52"/>
       <c r="B5" s="9">
         <v>45992</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="16">
         <v>135</v>
       </c>
       <c r="D5" s="6">
@@ -1641,13 +1582,13 @@
       <c r="H5" s="6">
         <v>21</v>
       </c>
-      <c r="I5" s="63">
-        <v>0</v>
-      </c>
-      <c r="J5" s="16">
+      <c r="I5" s="35">
+        <v>0</v>
+      </c>
+      <c r="J5" s="15">
         <v>9</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="16">
         <v>5</v>
       </c>
       <c r="L5" s="6">
@@ -1670,19 +1611,19 @@
         <v>15</v>
       </c>
       <c r="R5" s="6">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="S5" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A6" s="42"/>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="52"/>
       <c r="B6" s="9">
         <v>46023</v>
       </c>
-      <c r="C6" s="17">
-        <v>35</v>
+      <c r="C6" s="16">
+        <v>295</v>
       </c>
       <c r="D6" s="6">
         <v>419</v>
@@ -1699,13 +1640,13 @@
       <c r="H6" s="6">
         <v>3</v>
       </c>
-      <c r="I6" s="63">
-        <v>0</v>
-      </c>
-      <c r="J6" s="16">
+      <c r="I6" s="35">
+        <v>0</v>
+      </c>
+      <c r="J6" s="15">
         <v>12</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="16">
         <v>10</v>
       </c>
       <c r="L6" s="6">
@@ -1727,19 +1668,19 @@
         <v>18</v>
       </c>
       <c r="R6" s="6">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="S6" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A7" s="42"/>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="52"/>
       <c r="B7" s="9">
         <v>46054</v>
       </c>
-      <c r="C7" s="17">
-        <v>40</v>
+      <c r="C7" s="16">
+        <v>184</v>
       </c>
       <c r="D7" s="6">
         <v>312</v>
@@ -1756,14 +1697,14 @@
       <c r="H7" s="6">
         <v>0</v>
       </c>
-      <c r="I7" s="63">
+      <c r="I7" s="35">
         <f>1190+230</f>
         <v>1420</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>8</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="16">
         <v>8</v>
       </c>
       <c r="L7" s="6">
@@ -1785,18 +1726,18 @@
         <v>22</v>
       </c>
       <c r="R7" s="6">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="S7" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A8" s="42"/>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="52"/>
       <c r="B8" s="9">
         <v>46082</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <v>110</v>
       </c>
       <c r="D8" s="6">
@@ -1814,14 +1755,14 @@
       <c r="H8" s="6">
         <v>0</v>
       </c>
-      <c r="I8" s="63">
+      <c r="I8" s="35">
         <f>401+508</f>
         <v>909</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <v>6</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="16">
         <v>21</v>
       </c>
       <c r="L8" s="6">
@@ -1843,18 +1784,18 @@
         <v>8</v>
       </c>
       <c r="R8" s="6">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="S8" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A9" s="42"/>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="52"/>
       <c r="B9" s="9">
         <v>46113</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="16">
         <v>142</v>
       </c>
       <c r="D9" s="6">
@@ -1872,13 +1813,13 @@
       <c r="H9" s="6">
         <v>5</v>
       </c>
-      <c r="I9" s="63">
+      <c r="I9" s="35">
         <v>415</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="15">
         <v>8</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="16">
         <v>13</v>
       </c>
       <c r="L9" s="6">
@@ -1900,19 +1841,19 @@
         <v>13</v>
       </c>
       <c r="R9" s="6">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="S9" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A10" s="42"/>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="52"/>
       <c r="B10" s="9">
         <v>46143</v>
       </c>
-      <c r="C10" s="17">
-        <v>60</v>
+      <c r="C10" s="16">
+        <v>160</v>
       </c>
       <c r="D10" s="6">
         <v>210</v>
@@ -1929,13 +1870,13 @@
       <c r="H10" s="6">
         <v>0</v>
       </c>
-      <c r="I10" s="63">
-        <v>0</v>
-      </c>
-      <c r="J10" s="16">
+      <c r="I10" s="35">
+        <v>0</v>
+      </c>
+      <c r="J10" s="15">
         <v>33</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="16">
         <v>9</v>
       </c>
       <c r="L10" s="6">
@@ -1957,19 +1898,19 @@
         <v>0</v>
       </c>
       <c r="R10" s="6">
-        <v>187</v>
+        <v>287</v>
       </c>
       <c r="S10" s="6">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A11" s="42"/>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="52"/>
       <c r="B11" s="9">
         <v>46174</v>
       </c>
-      <c r="C11" s="17">
-        <v>86</v>
+      <c r="C11" s="16">
+        <v>219</v>
       </c>
       <c r="D11" s="6">
         <v>329</v>
@@ -1986,13 +1927,13 @@
       <c r="H11" s="6">
         <v>0</v>
       </c>
-      <c r="I11" s="63">
-        <v>0</v>
-      </c>
-      <c r="J11" s="16">
+      <c r="I11" s="35">
+        <v>0</v>
+      </c>
+      <c r="J11" s="15">
         <v>38</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="16">
         <v>8</v>
       </c>
       <c r="L11" s="6">
@@ -2014,19 +1955,19 @@
         <v>0</v>
       </c>
       <c r="R11" s="6">
-        <v>134</v>
+        <v>234</v>
       </c>
       <c r="S11" s="6">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="42"/>
+    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="52"/>
       <c r="B12" s="11">
         <v>46204</v>
       </c>
-      <c r="C12" s="20">
-        <v>39</v>
+      <c r="C12" s="18">
+        <v>149</v>
       </c>
       <c r="D12" s="7">
         <v>244</v>
@@ -2043,13 +1984,13 @@
       <c r="H12" s="7">
         <v>0</v>
       </c>
-      <c r="I12" s="64">
-        <v>0</v>
-      </c>
-      <c r="J12" s="19">
+      <c r="I12" s="36">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17">
         <v>58</v>
       </c>
-      <c r="K12" s="20">
+      <c r="K12" s="18">
         <v>10</v>
       </c>
       <c r="L12" s="7">
@@ -2071,95 +2012,95 @@
         <v>0</v>
       </c>
       <c r="R12" s="7">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="S12" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="65" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="43"/>
+    <row r="13" spans="1:19" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="53"/>
       <c r="B13" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="25">
         <f t="shared" ref="C13:S13" si="0">+C4+C5+C6+C7+C8+C9+C10+C11+C12</f>
-        <v>767</v>
-      </c>
-      <c r="D13" s="28">
+        <v>1514</v>
+      </c>
+      <c r="D13" s="23">
         <f t="shared" si="0"/>
         <v>2357</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="23">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="23">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="23">
         <f t="shared" si="0"/>
         <v>1495</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="23">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="23">
         <f t="shared" si="0"/>
         <v>2973</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="23">
         <f t="shared" si="0"/>
         <v>172</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="23">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="23">
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
-      <c r="M13" s="28">
+      <c r="M13" s="23">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="23">
         <f t="shared" si="0"/>
         <v>241</v>
       </c>
-      <c r="O13" s="28">
+      <c r="O13" s="23">
         <f t="shared" si="0"/>
         <v>1170</v>
       </c>
-      <c r="P13" s="28">
+      <c r="P13" s="23">
         <f t="shared" si="0"/>
         <v>696</v>
       </c>
-      <c r="Q13" s="28">
+      <c r="Q13" s="23">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="R13" s="28">
+      <c r="R13" s="23">
         <f t="shared" si="0"/>
-        <v>846</v>
-      </c>
-      <c r="S13" s="28">
+        <v>1747</v>
+      </c>
+      <c r="S13" s="23">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A14" s="40" t="s">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="50" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="9">
         <v>45962</v>
       </c>
-      <c r="C14" s="24">
-        <v>40</v>
+      <c r="C14" s="21">
+        <v>89</v>
       </c>
       <c r="D14" s="6">
         <v>137</v>
@@ -2176,14 +2117,14 @@
       <c r="H14" s="5">
         <v>25</v>
       </c>
-      <c r="I14" s="66">
+      <c r="I14" s="38">
         <f>529+630</f>
         <v>1159</v>
       </c>
-      <c r="J14" s="23">
-        <v>0</v>
-      </c>
-      <c r="K14" s="24">
+      <c r="J14" s="20">
+        <v>0</v>
+      </c>
+      <c r="K14" s="21">
         <v>10</v>
       </c>
       <c r="L14" s="5">
@@ -2206,19 +2147,19 @@
         <v>2</v>
       </c>
       <c r="R14" s="5">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="S14" s="5">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A15" s="40"/>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="50"/>
       <c r="B15" s="9">
         <v>45992</v>
       </c>
-      <c r="C15" s="17">
-        <v>20</v>
+      <c r="C15" s="16">
+        <v>35</v>
       </c>
       <c r="D15" s="6">
         <v>152</v>
@@ -2235,14 +2176,14 @@
       <c r="H15" s="6">
         <v>19</v>
       </c>
-      <c r="I15" s="63">
+      <c r="I15" s="35">
         <f>459+370</f>
         <v>829</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="15">
         <v>9</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="16">
         <v>6</v>
       </c>
       <c r="L15" s="6">
@@ -2265,19 +2206,19 @@
         <v>2</v>
       </c>
       <c r="R15" s="6">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="S15" s="6">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A16" s="40"/>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="50"/>
       <c r="B16" s="9">
         <v>46023</v>
       </c>
-      <c r="C16" s="17">
-        <v>22</v>
+      <c r="C16" s="16">
+        <v>142</v>
       </c>
       <c r="D16" s="6">
         <v>284</v>
@@ -2294,13 +2235,13 @@
       <c r="H16" s="6">
         <v>0</v>
       </c>
-      <c r="I16" s="63">
+      <c r="I16" s="35">
         <v>12</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="15">
         <v>23</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="16">
         <v>18</v>
       </c>
       <c r="L16" s="6">
@@ -2323,19 +2264,19 @@
         <v>0</v>
       </c>
       <c r="R16" s="6">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="S16" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A17" s="40"/>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="50"/>
       <c r="B17" s="9">
         <v>46054</v>
       </c>
-      <c r="C17" s="17">
-        <v>24</v>
+      <c r="C17" s="16">
+        <v>124</v>
       </c>
       <c r="D17" s="6">
         <v>282</v>
@@ -2352,13 +2293,13 @@
       <c r="H17" s="6">
         <v>13</v>
       </c>
-      <c r="I17" s="63">
+      <c r="I17" s="35">
         <v>190</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="15">
         <v>13</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="16">
         <v>16</v>
       </c>
       <c r="L17" s="6">
@@ -2381,18 +2322,18 @@
         <v>1</v>
       </c>
       <c r="R17" s="6">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="S17" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A18" s="40"/>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="50"/>
       <c r="B18" s="9">
         <v>46082</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="16">
         <v>104</v>
       </c>
       <c r="D18" s="6">
@@ -2410,13 +2351,13 @@
       <c r="H18" s="6">
         <v>3</v>
       </c>
-      <c r="I18" s="63">
+      <c r="I18" s="35">
         <v>30</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="15">
         <v>15</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="16">
         <v>20</v>
       </c>
       <c r="L18" s="6">
@@ -2439,19 +2380,19 @@
         <v>2</v>
       </c>
       <c r="R18" s="6">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="S18" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A19" s="40"/>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="50"/>
       <c r="B19" s="9">
         <v>46113</v>
       </c>
-      <c r="C19" s="17">
-        <v>110</v>
+      <c r="C19" s="16">
+        <v>210</v>
       </c>
       <c r="D19" s="6">
         <v>360</v>
@@ -2468,13 +2409,13 @@
       <c r="H19" s="6">
         <v>0</v>
       </c>
-      <c r="I19" s="63">
+      <c r="I19" s="35">
         <v>5</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="15">
         <v>31</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="16">
         <v>12</v>
       </c>
       <c r="L19" s="6">
@@ -2496,19 +2437,19 @@
         <v>3</v>
       </c>
       <c r="R19" s="6">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="S19" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A20" s="40"/>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="50"/>
       <c r="B20" s="9">
         <v>46143</v>
       </c>
-      <c r="C20" s="17">
-        <v>40</v>
+      <c r="C20" s="16">
+        <v>240</v>
       </c>
       <c r="D20" s="6">
         <v>439</v>
@@ -2525,13 +2466,13 @@
       <c r="H20" s="6">
         <v>0</v>
       </c>
-      <c r="I20" s="63">
+      <c r="I20" s="35">
         <v>35</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="15">
         <v>107</v>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="16">
         <v>10</v>
       </c>
       <c r="L20" s="6">
@@ -2553,19 +2494,19 @@
         <v>0</v>
       </c>
       <c r="R20" s="6">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="S20" s="6">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A21" s="40"/>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" s="50"/>
       <c r="B21" s="9">
         <v>46174</v>
       </c>
-      <c r="C21" s="17">
-        <v>20</v>
+      <c r="C21" s="16">
+        <v>168</v>
       </c>
       <c r="D21" s="6">
         <v>390</v>
@@ -2582,13 +2523,13 @@
       <c r="H21" s="6">
         <v>0</v>
       </c>
-      <c r="I21" s="63">
-        <v>0</v>
-      </c>
-      <c r="J21" s="16">
+      <c r="I21" s="35">
+        <v>0</v>
+      </c>
+      <c r="J21" s="15">
         <v>110</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="16">
         <v>17</v>
       </c>
       <c r="L21" s="6">
@@ -2610,19 +2551,19 @@
         <v>0</v>
       </c>
       <c r="R21" s="6">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="S21" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="40"/>
+    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="50"/>
       <c r="B22" s="11">
         <v>46204</v>
       </c>
-      <c r="C22" s="20">
-        <v>18</v>
+      <c r="C22" s="18">
+        <v>218</v>
       </c>
       <c r="D22" s="7">
         <v>246</v>
@@ -2630,7 +2571,7 @@
       <c r="E22" s="7">
         <v>0</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="33">
         <v>0</v>
       </c>
       <c r="G22" s="7">
@@ -2639,13 +2580,13 @@
       <c r="H22" s="7">
         <v>0</v>
       </c>
-      <c r="I22" s="64">
-        <v>0</v>
-      </c>
-      <c r="J22" s="19">
+      <c r="I22" s="36">
+        <v>0</v>
+      </c>
+      <c r="J22" s="17">
         <v>145</v>
       </c>
-      <c r="K22" s="20">
+      <c r="K22" s="18">
         <v>14</v>
       </c>
       <c r="L22" s="7">
@@ -2667,94 +2608,94 @@
         <v>0</v>
       </c>
       <c r="R22" s="7">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="S22" s="7">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="65" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="41"/>
+    <row r="23" spans="1:19" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="51"/>
       <c r="B23" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="25">
         <f t="shared" ref="C23:S23" si="1">+C14+C15+C16+C17+C18+C19+C20+C21+C22</f>
-        <v>398</v>
-      </c>
-      <c r="D23" s="28">
+        <v>1330</v>
+      </c>
+      <c r="D23" s="23">
         <f t="shared" si="1"/>
         <v>2514</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="23">
         <f t="shared" si="1"/>
         <v>1680</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="23">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="23">
         <f t="shared" si="1"/>
         <v>2260</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="23">
         <f t="shared" si="1"/>
         <v>453</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="23">
         <f t="shared" si="1"/>
         <v>123</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="23">
         <f t="shared" si="1"/>
         <v>158</v>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="23">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="23">
         <f t="shared" si="1"/>
         <v>127</v>
       </c>
-      <c r="O23" s="28">
+      <c r="O23" s="23">
         <f t="shared" si="1"/>
         <v>2600</v>
       </c>
-      <c r="P23" s="28">
+      <c r="P23" s="23">
         <f t="shared" si="1"/>
         <v>1800</v>
       </c>
-      <c r="Q23" s="28">
+      <c r="Q23" s="23">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="R23" s="28">
+      <c r="R23" s="23">
         <f t="shared" si="1"/>
-        <v>638</v>
-      </c>
-      <c r="S23" s="28">
+        <v>1539</v>
+      </c>
+      <c r="S23" s="23">
         <f t="shared" si="1"/>
         <v>223</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A24" s="40" t="s">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="50" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="9">
         <v>45962</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="21">
         <v>48</v>
       </c>
       <c r="D24" s="6">
@@ -2772,13 +2713,13 @@
       <c r="H24" s="5">
         <v>0</v>
       </c>
-      <c r="I24" s="66">
-        <v>0</v>
-      </c>
-      <c r="J24" s="23">
-        <v>0</v>
-      </c>
-      <c r="K24" s="24">
+      <c r="I24" s="38">
+        <v>0</v>
+      </c>
+      <c r="J24" s="20">
+        <v>0</v>
+      </c>
+      <c r="K24" s="21">
         <v>15</v>
       </c>
       <c r="L24" s="5">
@@ -2800,18 +2741,18 @@
         <v>0</v>
       </c>
       <c r="R24" s="5">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="S24" s="5">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A25" s="40"/>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="50"/>
       <c r="B25" s="9">
         <v>45992</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="16">
         <v>28</v>
       </c>
       <c r="D25" s="6">
@@ -2829,13 +2770,13 @@
       <c r="H25" s="6">
         <v>0</v>
       </c>
-      <c r="I25" s="63">
-        <v>0</v>
-      </c>
-      <c r="J25" s="16">
+      <c r="I25" s="35">
+        <v>0</v>
+      </c>
+      <c r="J25" s="15">
         <v>9</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="16">
         <v>22</v>
       </c>
       <c r="L25" s="6">
@@ -2857,18 +2798,18 @@
         <v>0</v>
       </c>
       <c r="R25" s="6">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="S25" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A26" s="40"/>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A26" s="50"/>
       <c r="B26" s="9">
         <v>46023</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="16">
         <v>30</v>
       </c>
       <c r="D26" s="6">
@@ -2886,13 +2827,13 @@
       <c r="H26" s="6">
         <v>0</v>
       </c>
-      <c r="I26" s="63">
-        <v>0</v>
-      </c>
-      <c r="J26" s="16">
+      <c r="I26" s="35">
+        <v>0</v>
+      </c>
+      <c r="J26" s="15">
         <v>18</v>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="16">
         <v>20</v>
       </c>
       <c r="L26" s="6">
@@ -2915,19 +2856,19 @@
         <v>2</v>
       </c>
       <c r="R26" s="6">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="S26" s="6">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A27" s="40"/>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A27" s="50"/>
       <c r="B27" s="9">
         <v>46054</v>
       </c>
-      <c r="C27" s="17">
-        <v>32</v>
+      <c r="C27" s="16">
+        <v>72</v>
       </c>
       <c r="D27" s="6">
         <v>102</v>
@@ -2944,13 +2885,13 @@
       <c r="H27" s="6">
         <v>0</v>
       </c>
-      <c r="I27" s="63">
-        <v>0</v>
-      </c>
-      <c r="J27" s="16">
+      <c r="I27" s="35">
+        <v>0</v>
+      </c>
+      <c r="J27" s="15">
         <v>16</v>
       </c>
-      <c r="K27" s="17">
+      <c r="K27" s="16">
         <v>15</v>
       </c>
       <c r="L27" s="6">
@@ -2972,18 +2913,18 @@
         <v>4</v>
       </c>
       <c r="R27" s="6">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="S27" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="40"/>
+    <row r="28" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="50"/>
       <c r="B28" s="9">
         <v>46082</v>
       </c>
-      <c r="C28" s="67">
+      <c r="C28" s="39">
         <v>102</v>
       </c>
       <c r="D28" s="6">
@@ -3001,13 +2942,13 @@
       <c r="H28" s="6">
         <v>10</v>
       </c>
-      <c r="I28" s="63">
-        <v>0</v>
-      </c>
-      <c r="J28" s="16">
+      <c r="I28" s="35">
+        <v>0</v>
+      </c>
+      <c r="J28" s="15">
         <v>26</v>
       </c>
-      <c r="K28" s="17">
+      <c r="K28" s="16">
         <v>12</v>
       </c>
       <c r="L28" s="6">
@@ -3029,18 +2970,18 @@
         <v>1</v>
       </c>
       <c r="R28" s="6">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="S28" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A29" s="40"/>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" s="50"/>
       <c r="B29" s="9">
         <v>46113</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="16">
         <v>119</v>
       </c>
       <c r="D29" s="6">
@@ -3058,13 +2999,13 @@
       <c r="H29" s="6">
         <v>0</v>
       </c>
-      <c r="I29" s="63">
-        <v>0</v>
-      </c>
-      <c r="J29" s="16">
+      <c r="I29" s="35">
+        <v>0</v>
+      </c>
+      <c r="J29" s="15">
         <v>16</v>
       </c>
-      <c r="K29" s="17">
+      <c r="K29" s="16">
         <v>17</v>
       </c>
       <c r="L29" s="6">
@@ -3086,19 +3027,19 @@
         <v>5</v>
       </c>
       <c r="R29" s="6">
-        <v>85</v>
+        <v>185</v>
       </c>
       <c r="S29" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A30" s="40"/>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A30" s="50"/>
       <c r="B30" s="9">
         <v>46143</v>
       </c>
-      <c r="C30" s="17">
-        <v>48</v>
+      <c r="C30" s="16">
+        <v>168</v>
       </c>
       <c r="D30" s="6">
         <v>204</v>
@@ -3115,13 +3056,13 @@
       <c r="H30" s="6">
         <v>30</v>
       </c>
-      <c r="I30" s="63">
-        <v>0</v>
-      </c>
-      <c r="J30" s="16">
+      <c r="I30" s="35">
+        <v>0</v>
+      </c>
+      <c r="J30" s="15">
         <v>76</v>
       </c>
-      <c r="K30" s="17">
+      <c r="K30" s="16">
         <v>20</v>
       </c>
       <c r="L30" s="6">
@@ -3143,19 +3084,19 @@
         <v>0</v>
       </c>
       <c r="R30" s="6">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="S30" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A31" s="40"/>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A31" s="50"/>
       <c r="B31" s="9">
         <v>46174</v>
       </c>
-      <c r="C31" s="17">
-        <v>26</v>
+      <c r="C31" s="16">
+        <v>126</v>
       </c>
       <c r="D31" s="6">
         <v>215</v>
@@ -3172,13 +3113,13 @@
       <c r="H31" s="6">
         <v>0</v>
       </c>
-      <c r="I31" s="63">
-        <v>0</v>
-      </c>
-      <c r="J31" s="16">
+      <c r="I31" s="35">
+        <v>0</v>
+      </c>
+      <c r="J31" s="15">
         <v>96</v>
       </c>
-      <c r="K31" s="17">
+      <c r="K31" s="16">
         <v>8</v>
       </c>
       <c r="L31" s="6">
@@ -3201,19 +3142,19 @@
         <v>0</v>
       </c>
       <c r="R31" s="6">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="S31" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="40"/>
+    <row r="32" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="50"/>
       <c r="B32" s="9">
         <v>46204</v>
       </c>
-      <c r="C32" s="67">
-        <v>28</v>
+      <c r="C32" s="39">
+        <v>88</v>
       </c>
       <c r="D32" s="7">
         <v>232</v>
@@ -3228,13 +3169,13 @@
       <c r="H32" s="8">
         <v>0</v>
       </c>
-      <c r="I32" s="68">
-        <v>0</v>
-      </c>
-      <c r="J32" s="69">
+      <c r="I32" s="40">
+        <v>0</v>
+      </c>
+      <c r="J32" s="41">
         <v>85</v>
       </c>
-      <c r="K32" s="67">
+      <c r="K32" s="39">
         <v>13</v>
       </c>
       <c r="L32" s="8">
@@ -3256,95 +3197,95 @@
         <v>1</v>
       </c>
       <c r="R32" s="8">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="S32" s="8">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:19" s="65" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="41"/>
+    <row r="33" spans="1:19" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="51"/>
       <c r="B33" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="25">
         <f t="shared" ref="C33:S33" si="2">+C24+C25+C26+C27+C28+C29+C30+C31+C32</f>
-        <v>461</v>
-      </c>
-      <c r="D33" s="28">
+        <v>781</v>
+      </c>
+      <c r="D33" s="23">
         <f t="shared" si="2"/>
         <v>1127</v>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="23">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="23">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="23">
         <f t="shared" si="2"/>
         <v>1470</v>
       </c>
-      <c r="H33" s="28">
+      <c r="H33" s="23">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="I33" s="28">
+      <c r="I33" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J33" s="28">
+      <c r="J33" s="23">
         <f t="shared" si="2"/>
         <v>342</v>
       </c>
-      <c r="K33" s="28">
+      <c r="K33" s="23">
         <f t="shared" si="2"/>
         <v>142</v>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="23">
         <f t="shared" si="2"/>
         <v>289</v>
       </c>
-      <c r="M33" s="28">
+      <c r="M33" s="23">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="N33" s="28">
+      <c r="N33" s="23">
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="O33" s="28">
+      <c r="O33" s="23">
         <f t="shared" si="2"/>
         <v>3088</v>
       </c>
-      <c r="P33" s="28">
+      <c r="P33" s="23">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="Q33" s="28">
+      <c r="Q33" s="23">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="R33" s="28">
+      <c r="R33" s="23">
         <f t="shared" si="2"/>
-        <v>545</v>
-      </c>
-      <c r="S33" s="28">
+        <v>1445</v>
+      </c>
+      <c r="S33" s="23">
         <f t="shared" si="2"/>
         <v>187</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A34" s="40" t="s">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="50" t="s">
         <v>24</v>
       </c>
       <c r="B34" s="9">
         <v>45962</v>
       </c>
-      <c r="C34" s="70">
-        <v>15</v>
+      <c r="C34" s="42">
+        <v>109</v>
       </c>
       <c r="D34" s="7">
         <v>180</v>
@@ -3361,16 +3302,16 @@
       <c r="H34" s="5">
         <v>0</v>
       </c>
-      <c r="I34" s="66">
+      <c r="I34" s="38">
         <v>220</v>
       </c>
-      <c r="J34" s="23">
-        <v>0</v>
-      </c>
-      <c r="K34" s="24">
+      <c r="J34" s="20">
+        <v>0</v>
+      </c>
+      <c r="K34" s="21">
         <v>20</v>
       </c>
-      <c r="L34" s="24">
+      <c r="L34" s="21">
         <v>35</v>
       </c>
       <c r="M34" s="5">
@@ -3389,18 +3330,18 @@
         <v>0</v>
       </c>
       <c r="R34" s="5">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="S34" s="5">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A35" s="40"/>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" s="50"/>
       <c r="B35" s="9">
         <v>45992</v>
       </c>
-      <c r="C35" s="71">
+      <c r="C35" s="43">
         <v>45</v>
       </c>
       <c r="D35" s="6">
@@ -3418,17 +3359,17 @@
       <c r="H35" s="6">
         <v>30</v>
       </c>
-      <c r="I35" s="63">
+      <c r="I35" s="35">
         <f>136+780+358</f>
         <v>1274</v>
       </c>
-      <c r="J35" s="16">
+      <c r="J35" s="15">
         <v>16</v>
       </c>
-      <c r="K35" s="17">
+      <c r="K35" s="16">
         <v>17</v>
       </c>
-      <c r="L35" s="17">
+      <c r="L35" s="16">
         <v>30</v>
       </c>
       <c r="M35" s="6">
@@ -3448,19 +3389,19 @@
         <v>5</v>
       </c>
       <c r="R35" s="6">
-        <v>115</v>
+        <v>215</v>
       </c>
       <c r="S35" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A36" s="40"/>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" s="50"/>
       <c r="B36" s="9">
         <v>46023</v>
       </c>
-      <c r="C36" s="71">
-        <v>35</v>
+      <c r="C36" s="43">
+        <v>94</v>
       </c>
       <c r="D36" s="6">
         <v>116</v>
@@ -3477,16 +3418,16 @@
       <c r="H36" s="6">
         <v>0</v>
       </c>
-      <c r="I36" s="63">
-        <v>0</v>
-      </c>
-      <c r="J36" s="16">
+      <c r="I36" s="35">
+        <v>0</v>
+      </c>
+      <c r="J36" s="15">
         <v>29</v>
       </c>
-      <c r="K36" s="17">
+      <c r="K36" s="16">
         <v>20</v>
       </c>
-      <c r="L36" s="17">
+      <c r="L36" s="16">
         <v>60</v>
       </c>
       <c r="M36" s="6">
@@ -3505,19 +3446,19 @@
         <v>2</v>
       </c>
       <c r="R36" s="6">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="S36" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A37" s="40"/>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A37" s="50"/>
       <c r="B37" s="9">
         <v>46054</v>
       </c>
-      <c r="C37" s="71">
-        <v>43</v>
+      <c r="C37" s="43">
+        <v>113</v>
       </c>
       <c r="D37" s="6">
         <v>166</v>
@@ -3534,14 +3475,14 @@
       <c r="H37" s="6">
         <v>0</v>
       </c>
-      <c r="I37" s="63">
+      <c r="I37" s="35">
         <f>264+70</f>
         <v>334</v>
       </c>
-      <c r="J37" s="16">
+      <c r="J37" s="15">
         <v>11</v>
       </c>
-      <c r="K37" s="17">
+      <c r="K37" s="16">
         <v>25</v>
       </c>
       <c r="L37" s="6">
@@ -3563,19 +3504,19 @@
         <v>2</v>
       </c>
       <c r="R37" s="6">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="S37" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A38" s="40"/>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A38" s="50"/>
       <c r="B38" s="9">
         <v>46082</v>
       </c>
-      <c r="C38" s="71">
-        <v>55</v>
+      <c r="C38" s="43">
+        <v>255</v>
       </c>
       <c r="D38" s="6">
         <f>374-67</f>
@@ -3593,14 +3534,14 @@
       <c r="H38" s="6">
         <v>220</v>
       </c>
-      <c r="I38" s="63">
+      <c r="I38" s="35">
         <f>450+72</f>
         <v>522</v>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="15">
         <v>15</v>
       </c>
-      <c r="K38" s="17">
+      <c r="K38" s="16">
         <v>14</v>
       </c>
       <c r="L38" s="6">
@@ -3622,19 +3563,19 @@
         <v>7</v>
       </c>
       <c r="R38" s="6">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="S38" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A39" s="40"/>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A39" s="50"/>
       <c r="B39" s="9">
         <v>46113</v>
       </c>
-      <c r="C39" s="17">
-        <v>60</v>
+      <c r="C39" s="16">
+        <v>160</v>
       </c>
       <c r="D39" s="6">
         <v>384</v>
@@ -3651,13 +3592,13 @@
       <c r="H39" s="6">
         <v>100</v>
       </c>
-      <c r="I39" s="63">
+      <c r="I39" s="35">
         <v>630</v>
       </c>
-      <c r="J39" s="16">
+      <c r="J39" s="15">
         <v>22</v>
       </c>
-      <c r="K39" s="17">
+      <c r="K39" s="16">
         <v>10</v>
       </c>
       <c r="L39" s="6">
@@ -3679,19 +3620,19 @@
         <v>1</v>
       </c>
       <c r="R39" s="6">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="S39" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A40" s="40"/>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A40" s="50"/>
       <c r="B40" s="9">
         <v>46143</v>
       </c>
-      <c r="C40" s="17">
-        <v>82</v>
+      <c r="C40" s="16">
+        <v>282</v>
       </c>
       <c r="D40" s="6">
         <v>435</v>
@@ -3708,13 +3649,13 @@
       <c r="H40" s="6">
         <v>0</v>
       </c>
-      <c r="I40" s="63">
+      <c r="I40" s="35">
         <v>504</v>
       </c>
-      <c r="J40" s="16">
+      <c r="J40" s="15">
         <v>58</v>
       </c>
-      <c r="K40" s="17">
+      <c r="K40" s="16">
         <v>12</v>
       </c>
       <c r="L40" s="6">
@@ -3736,19 +3677,19 @@
         <v>5</v>
       </c>
       <c r="R40" s="6">
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="S40" s="6">
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A41" s="40"/>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A41" s="50"/>
       <c r="B41" s="9">
         <v>46174</v>
       </c>
-      <c r="C41" s="17">
-        <v>87</v>
+      <c r="C41" s="16">
+        <v>187</v>
       </c>
       <c r="D41" s="6">
         <v>334</v>
@@ -3765,13 +3706,13 @@
       <c r="H41" s="6">
         <v>0</v>
       </c>
-      <c r="I41" s="63">
-        <v>0</v>
-      </c>
-      <c r="J41" s="16">
+      <c r="I41" s="35">
+        <v>0</v>
+      </c>
+      <c r="J41" s="15">
         <v>73</v>
       </c>
-      <c r="K41" s="17">
+      <c r="K41" s="16">
         <v>15</v>
       </c>
       <c r="L41" s="6">
@@ -3793,18 +3734,18 @@
         <v>0</v>
       </c>
       <c r="R41" s="6">
-        <v>125</v>
+        <v>239</v>
       </c>
       <c r="S41" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="40"/>
+    <row r="42" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="50"/>
       <c r="B42" s="9">
         <v>46204</v>
       </c>
-      <c r="C42" s="67">
+      <c r="C42" s="39">
         <v>110</v>
       </c>
       <c r="D42" s="7">
@@ -3822,13 +3763,13 @@
       <c r="H42" s="8">
         <v>0</v>
       </c>
-      <c r="I42" s="68">
-        <v>0</v>
-      </c>
-      <c r="J42" s="69">
+      <c r="I42" s="40">
+        <v>0</v>
+      </c>
+      <c r="J42" s="41">
         <v>91</v>
       </c>
-      <c r="K42" s="67">
+      <c r="K42" s="39">
         <v>10</v>
       </c>
       <c r="L42" s="8">
@@ -3850,95 +3791,95 @@
         <v>0</v>
       </c>
       <c r="R42" s="8">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="S42" s="8">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:19" s="65" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="41"/>
+    <row r="43" spans="1:19" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="51"/>
       <c r="B43" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="25">
         <f t="shared" ref="C43:S43" si="3">+C34+C35+C36+C37+C38+C39+C40+C41+C42</f>
-        <v>532</v>
-      </c>
-      <c r="D43" s="28">
+        <v>1355</v>
+      </c>
+      <c r="D43" s="23">
         <f t="shared" si="3"/>
         <v>2255</v>
       </c>
-      <c r="E43" s="28">
+      <c r="E43" s="23">
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-      <c r="F43" s="28">
+      <c r="F43" s="23">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="G43" s="28">
+      <c r="G43" s="23">
         <f t="shared" si="3"/>
         <v>2700</v>
       </c>
-      <c r="H43" s="28">
+      <c r="H43" s="23">
         <f t="shared" si="3"/>
         <v>350</v>
       </c>
-      <c r="I43" s="28">
+      <c r="I43" s="23">
         <f t="shared" si="3"/>
         <v>3484</v>
       </c>
-      <c r="J43" s="28">
+      <c r="J43" s="23">
         <f t="shared" si="3"/>
         <v>315</v>
       </c>
-      <c r="K43" s="28">
+      <c r="K43" s="23">
         <f t="shared" si="3"/>
         <v>143</v>
       </c>
-      <c r="L43" s="28">
+      <c r="L43" s="23">
         <f t="shared" si="3"/>
         <v>383</v>
       </c>
-      <c r="M43" s="28">
+      <c r="M43" s="23">
         <f t="shared" si="3"/>
         <v>107</v>
       </c>
-      <c r="N43" s="28">
+      <c r="N43" s="23">
         <f t="shared" si="3"/>
         <v>325</v>
       </c>
-      <c r="O43" s="28">
+      <c r="O43" s="23">
         <f t="shared" si="3"/>
         <v>1330</v>
       </c>
-      <c r="P43" s="28">
+      <c r="P43" s="23">
         <f t="shared" si="3"/>
         <v>1500</v>
       </c>
-      <c r="Q43" s="28">
+      <c r="Q43" s="23">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="R43" s="28">
+      <c r="R43" s="23">
         <f t="shared" si="3"/>
-        <v>890</v>
-      </c>
-      <c r="S43" s="28">
+        <v>1804</v>
+      </c>
+      <c r="S43" s="23">
         <f t="shared" si="3"/>
         <v>210</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A44" s="40" t="s">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A44" s="50" t="s">
         <v>25</v>
       </c>
       <c r="B44" s="9">
         <v>45962</v>
       </c>
-      <c r="C44" s="24">
-        <v>30</v>
+      <c r="C44" s="21">
+        <v>58</v>
       </c>
       <c r="D44" s="5">
         <v>160</v>
@@ -3955,14 +3896,14 @@
       <c r="H44" s="5">
         <v>87</v>
       </c>
-      <c r="I44" s="66">
+      <c r="I44" s="38">
         <f>540+250+165</f>
         <v>955</v>
       </c>
-      <c r="J44" s="23">
-        <v>0</v>
-      </c>
-      <c r="K44" s="24">
+      <c r="J44" s="20">
+        <v>0</v>
+      </c>
+      <c r="K44" s="21">
         <v>12</v>
       </c>
       <c r="L44" s="5">
@@ -3985,18 +3926,18 @@
         <v>0</v>
       </c>
       <c r="R44" s="5">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="S44" s="5">
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A45" s="40"/>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A45" s="50"/>
       <c r="B45" s="9">
         <v>45992</v>
       </c>
-      <c r="C45" s="17">
+      <c r="C45" s="16">
         <v>102</v>
       </c>
       <c r="D45" s="6">
@@ -4014,13 +3955,13 @@
       <c r="H45" s="6">
         <v>5</v>
       </c>
-      <c r="I45" s="63">
+      <c r="I45" s="35">
         <v>100</v>
       </c>
-      <c r="J45" s="16">
+      <c r="J45" s="15">
         <v>16</v>
       </c>
-      <c r="K45" s="17">
+      <c r="K45" s="16">
         <v>13</v>
       </c>
       <c r="L45" s="6">
@@ -4042,19 +3983,19 @@
         <v>2</v>
       </c>
       <c r="R45" s="6">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="S45" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A46" s="40"/>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A46" s="50"/>
       <c r="B46" s="9">
         <v>46023</v>
       </c>
-      <c r="C46" s="17">
-        <v>58</v>
+      <c r="C46" s="16">
+        <v>358</v>
       </c>
       <c r="D46" s="6">
         <v>347</v>
@@ -4071,13 +4012,13 @@
       <c r="H46" s="6">
         <v>0</v>
       </c>
-      <c r="I46" s="63">
-        <v>0</v>
-      </c>
-      <c r="J46" s="16">
+      <c r="I46" s="35">
+        <v>0</v>
+      </c>
+      <c r="J46" s="15">
         <v>11</v>
       </c>
-      <c r="K46" s="17">
+      <c r="K46" s="16">
         <v>10</v>
       </c>
       <c r="L46" s="6">
@@ -4099,19 +4040,19 @@
         <v>1</v>
       </c>
       <c r="R46" s="6">
-        <v>105</v>
+        <v>205</v>
       </c>
       <c r="S46" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A47" s="40"/>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47" s="50"/>
       <c r="B47" s="9">
         <v>46054</v>
       </c>
-      <c r="C47" s="17">
-        <v>65</v>
+      <c r="C47" s="16">
+        <v>365</v>
       </c>
       <c r="D47" s="6">
         <v>412</v>
@@ -4128,13 +4069,13 @@
       <c r="H47" s="6">
         <v>16</v>
       </c>
-      <c r="I47" s="63">
+      <c r="I47" s="35">
         <v>555</v>
       </c>
-      <c r="J47" s="16">
+      <c r="J47" s="15">
         <v>15</v>
       </c>
-      <c r="K47" s="17">
+      <c r="K47" s="16">
         <v>13</v>
       </c>
       <c r="L47" s="6">
@@ -4157,18 +4098,18 @@
         <v>1</v>
       </c>
       <c r="R47" s="6">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="S47" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A48" s="40"/>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A48" s="50"/>
       <c r="B48" s="9">
         <v>46082</v>
       </c>
-      <c r="C48" s="17">
+      <c r="C48" s="16">
         <v>70</v>
       </c>
       <c r="D48" s="6">
@@ -4186,13 +4127,13 @@
       <c r="H48" s="6">
         <v>0</v>
       </c>
-      <c r="I48" s="63">
-        <v>0</v>
-      </c>
-      <c r="J48" s="16">
+      <c r="I48" s="35">
+        <v>0</v>
+      </c>
+      <c r="J48" s="15">
         <v>33</v>
       </c>
-      <c r="K48" s="17">
+      <c r="K48" s="16">
         <v>26</v>
       </c>
       <c r="L48" s="6">
@@ -4214,18 +4155,18 @@
         <v>0</v>
       </c>
       <c r="R48" s="6">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="S48" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A49" s="40"/>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49" s="50"/>
       <c r="B49" s="9">
         <v>46113</v>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="16">
         <v>52</v>
       </c>
       <c r="D49" s="6">
@@ -4243,13 +4184,13 @@
       <c r="H49" s="6">
         <v>0</v>
       </c>
-      <c r="I49" s="63">
+      <c r="I49" s="35">
         <v>200</v>
       </c>
-      <c r="J49" s="16">
+      <c r="J49" s="15">
         <v>26</v>
       </c>
-      <c r="K49" s="17">
+      <c r="K49" s="16">
         <v>10</v>
       </c>
       <c r="L49" s="6">
@@ -4271,19 +4212,19 @@
         <v>0</v>
       </c>
       <c r="R49" s="6">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="S49" s="6">
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A50" s="40"/>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50" s="50"/>
       <c r="B50" s="9">
         <v>46143</v>
       </c>
-      <c r="C50" s="17">
-        <v>48</v>
+      <c r="C50" s="16">
+        <v>188</v>
       </c>
       <c r="D50" s="6">
         <v>285</v>
@@ -4300,13 +4241,13 @@
       <c r="H50" s="6">
         <v>13</v>
       </c>
-      <c r="I50" s="63">
+      <c r="I50" s="35">
         <v>210</v>
       </c>
-      <c r="J50" s="16">
+      <c r="J50" s="15">
         <v>69</v>
       </c>
-      <c r="K50" s="17">
+      <c r="K50" s="16">
         <v>17</v>
       </c>
       <c r="L50" s="6">
@@ -4328,19 +4269,19 @@
         <v>2</v>
       </c>
       <c r="R50" s="6">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="S50" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A51" s="40"/>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51" s="50"/>
       <c r="B51" s="9">
         <v>46174</v>
       </c>
-      <c r="C51" s="17">
-        <v>20</v>
+      <c r="C51" s="16">
+        <v>259</v>
       </c>
       <c r="D51" s="6">
         <v>393</v>
@@ -4357,13 +4298,13 @@
       <c r="H51" s="6">
         <v>0</v>
       </c>
-      <c r="I51" s="63">
-        <v>0</v>
-      </c>
-      <c r="J51" s="16">
+      <c r="I51" s="35">
+        <v>0</v>
+      </c>
+      <c r="J51" s="15">
         <v>81</v>
       </c>
-      <c r="K51" s="17">
+      <c r="K51" s="16">
         <v>7</v>
       </c>
       <c r="L51" s="6">
@@ -4385,19 +4326,19 @@
         <v>1</v>
       </c>
       <c r="R51" s="6">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="S51" s="6">
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="40"/>
+    <row r="52" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="50"/>
       <c r="B52" s="9">
         <v>46204</v>
       </c>
-      <c r="C52" s="67">
-        <v>30</v>
+      <c r="C52" s="39">
+        <v>203</v>
       </c>
       <c r="D52" s="7">
         <v>233</v>
@@ -4414,13 +4355,13 @@
       <c r="H52" s="8">
         <v>12</v>
       </c>
-      <c r="I52" s="68">
+      <c r="I52" s="40">
         <v>150</v>
       </c>
-      <c r="J52" s="69">
+      <c r="J52" s="41">
         <v>85</v>
       </c>
-      <c r="K52" s="67">
+      <c r="K52" s="39">
         <v>15</v>
       </c>
       <c r="L52" s="8">
@@ -4442,156 +4383,156 @@
         <v>1</v>
       </c>
       <c r="R52" s="8">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="S52" s="8">
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:19" s="65" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="40"/>
+    <row r="53" spans="1:19" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="50"/>
       <c r="B53" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C53" s="30">
+      <c r="C53" s="25">
         <f t="shared" ref="C53:S53" si="4">+C44+C45+C46+C47+C48+C49+C50+C51+C52</f>
-        <v>475</v>
-      </c>
-      <c r="D53" s="28">
+        <v>1655</v>
+      </c>
+      <c r="D53" s="23">
         <f t="shared" si="4"/>
         <v>2236</v>
       </c>
-      <c r="E53" s="28">
+      <c r="E53" s="23">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="F53" s="28">
+      <c r="F53" s="23">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="G53" s="28">
+      <c r="G53" s="23">
         <f t="shared" si="4"/>
         <v>800</v>
       </c>
-      <c r="H53" s="28">
+      <c r="H53" s="23">
         <f t="shared" si="4"/>
         <v>133</v>
       </c>
-      <c r="I53" s="28">
+      <c r="I53" s="23">
         <f t="shared" si="4"/>
         <v>2170</v>
       </c>
-      <c r="J53" s="28">
+      <c r="J53" s="23">
         <f t="shared" si="4"/>
         <v>336</v>
       </c>
-      <c r="K53" s="28">
+      <c r="K53" s="23">
         <f t="shared" si="4"/>
         <v>123</v>
       </c>
-      <c r="L53" s="28">
+      <c r="L53" s="23">
         <f t="shared" si="4"/>
         <v>507</v>
       </c>
-      <c r="M53" s="28">
+      <c r="M53" s="23">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="N53" s="28">
+      <c r="N53" s="23">
         <f t="shared" si="4"/>
         <v>164</v>
       </c>
-      <c r="O53" s="28">
+      <c r="O53" s="23">
         <f t="shared" si="4"/>
         <v>1550</v>
       </c>
-      <c r="P53" s="28">
+      <c r="P53" s="23">
         <f t="shared" si="4"/>
         <v>1000</v>
       </c>
-      <c r="Q53" s="28">
+      <c r="Q53" s="23">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="R53" s="28">
+      <c r="R53" s="23">
         <f t="shared" si="4"/>
-        <v>850</v>
-      </c>
-      <c r="S53" s="28">
+        <v>1750</v>
+      </c>
+      <c r="S53" s="23">
         <f t="shared" si="4"/>
         <v>189</v>
       </c>
     </row>
-    <row r="54" spans="1:19" s="65" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="44" t="s">
+    <row r="54" spans="1:19" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="B54" s="45"/>
-      <c r="C54" s="72">
+      <c r="B54" s="55"/>
+      <c r="C54" s="44">
         <f t="shared" ref="C54:S54" si="5">+C53+C43+C33+C23+C13</f>
-        <v>2633</v>
-      </c>
-      <c r="D54" s="72">
+        <v>6635</v>
+      </c>
+      <c r="D54" s="44">
         <f t="shared" si="5"/>
         <v>10489</v>
       </c>
-      <c r="E54" s="72">
+      <c r="E54" s="44">
         <f t="shared" si="5"/>
         <v>104</v>
       </c>
-      <c r="F54" s="72">
+      <c r="F54" s="44">
         <f t="shared" si="5"/>
         <v>85</v>
       </c>
-      <c r="G54" s="72">
+      <c r="G54" s="44">
         <f t="shared" si="5"/>
         <v>8145</v>
       </c>
-      <c r="H54" s="72">
+      <c r="H54" s="44">
         <f t="shared" si="5"/>
         <v>612</v>
       </c>
-      <c r="I54" s="72">
+      <c r="I54" s="44">
         <f t="shared" si="5"/>
         <v>10887</v>
       </c>
-      <c r="J54" s="72">
+      <c r="J54" s="44">
         <f t="shared" si="5"/>
         <v>1618</v>
       </c>
-      <c r="K54" s="72">
+      <c r="K54" s="44">
         <f t="shared" si="5"/>
         <v>625</v>
       </c>
-      <c r="L54" s="72">
+      <c r="L54" s="44">
         <f t="shared" si="5"/>
         <v>1448</v>
       </c>
-      <c r="M54" s="72">
+      <c r="M54" s="44">
         <f t="shared" si="5"/>
         <v>211</v>
       </c>
-      <c r="N54" s="72">
+      <c r="N54" s="44">
         <f t="shared" si="5"/>
         <v>904</v>
       </c>
-      <c r="O54" s="72">
+      <c r="O54" s="44">
         <f t="shared" si="5"/>
         <v>9738</v>
       </c>
-      <c r="P54" s="72">
+      <c r="P54" s="44">
         <f t="shared" si="5"/>
         <v>5996</v>
       </c>
-      <c r="Q54" s="72">
+      <c r="Q54" s="44">
         <f t="shared" si="5"/>
         <v>134</v>
       </c>
-      <c r="R54" s="72">
+      <c r="R54" s="44">
         <f t="shared" si="5"/>
-        <v>3769</v>
-      </c>
-      <c r="S54" s="72">
+        <v>8285</v>
+      </c>
+      <c r="S54" s="44">
         <f t="shared" si="5"/>
         <v>972</v>
       </c>
@@ -4619,76 +4560,76 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5390366C-FAC4-4AD0-96A6-FA3137F03C20}">
   <dimension ref="A1:Q54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.453125" style="62" customWidth="1"/>
-    <col min="2" max="2" width="10.1796875" style="62" customWidth="1"/>
-    <col min="3" max="3" width="11.08984375" style="62" customWidth="1"/>
-    <col min="4" max="6" width="8.7265625" style="62"/>
-    <col min="7" max="8" width="9" style="62" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="62" customWidth="1"/>
-    <col min="10" max="10" width="13.54296875" style="62" customWidth="1"/>
-    <col min="11" max="11" width="11.36328125" style="62" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="13.81640625" style="62" customWidth="1"/>
-    <col min="13" max="13" width="14.1796875" style="62" customWidth="1"/>
-    <col min="14" max="14" width="11.453125" style="62" customWidth="1"/>
-    <col min="15" max="15" width="14.6328125" style="62" customWidth="1"/>
-    <col min="16" max="16" width="12.453125" style="62" customWidth="1"/>
-    <col min="17" max="17" width="12.6328125" style="62" customWidth="1"/>
-    <col min="18" max="16384" width="8.7265625" style="62"/>
+    <col min="1" max="1" width="23.44140625" style="34" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" style="34" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="34" customWidth="1"/>
+    <col min="4" max="6" width="8.77734375" style="34"/>
+    <col min="7" max="8" width="9" style="34" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="34" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" style="34" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" style="34" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="13.77734375" style="34" customWidth="1"/>
+    <col min="13" max="13" width="14.21875" style="34" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" style="34" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" style="34" customWidth="1"/>
+    <col min="16" max="16" width="12.44140625" style="34" customWidth="1"/>
+    <col min="17" max="17" width="12.6640625" style="34" customWidth="1"/>
+    <col min="18" max="16384" width="8.77734375" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:17" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-    </row>
-    <row r="2" spans="1:17" ht="21.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="46" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+    </row>
+    <row r="2" spans="1:17" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="77" t="s">
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-    </row>
-    <row r="3" spans="1:17" ht="73" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="47"/>
-      <c r="B3" s="51"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+    </row>
+    <row r="3" spans="1:17" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="61"/>
+      <c r="B3" s="71"/>
       <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
@@ -4735,15 +4676,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="42" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="52" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="12">
         <v>45962</v>
       </c>
-      <c r="C4" s="26">
-        <v>180</v>
+      <c r="C4" s="16">
+        <v>120</v>
       </c>
       <c r="D4" s="5">
         <v>84</v>
@@ -4757,10 +4698,10 @@
       <c r="G4" s="5">
         <v>80</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="20">
         <v>1000</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="28">
         <v>90</v>
       </c>
       <c r="J4" s="5">
@@ -4775,10 +4716,10 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="65">
         <v>2500</v>
       </c>
-      <c r="O4" s="52">
+      <c r="O4" s="65">
         <v>2000</v>
       </c>
       <c r="P4" s="5">
@@ -4788,13 +4729,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A5" s="42"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="52"/>
       <c r="B5" s="12">
         <v>45992</v>
       </c>
-      <c r="C5" s="15">
-        <v>185</v>
+      <c r="C5" s="16">
+        <v>135</v>
       </c>
       <c r="D5" s="6">
         <v>180</v>
@@ -4808,10 +4749,10 @@
       <c r="G5" s="6">
         <v>100</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>1000</v>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="26">
         <v>110</v>
       </c>
       <c r="J5" s="6">
@@ -4827,8 +4768,8 @@
         <f>18+27</f>
         <v>45</v>
       </c>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="66"/>
       <c r="P5" s="6">
         <v>15</v>
       </c>
@@ -4836,13 +4777,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A6" s="42"/>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="52"/>
       <c r="B6" s="12">
         <v>46023</v>
       </c>
-      <c r="C6" s="15">
-        <v>150</v>
+      <c r="C6" s="16">
+        <v>295</v>
       </c>
       <c r="D6" s="6">
         <v>419</v>
@@ -4856,14 +4797,14 @@
       <c r="G6" s="6">
         <v>70</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="15">
         <v>1000</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="26">
         <v>240</v>
       </c>
       <c r="J6" s="6">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="K6" s="6">
         <v>50</v>
@@ -4874,8 +4815,8 @@
       <c r="M6" s="6">
         <v>0</v>
       </c>
-      <c r="N6" s="53"/>
-      <c r="O6" s="53"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
       <c r="P6" s="6">
         <v>18</v>
       </c>
@@ -4883,13 +4824,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A7" s="42"/>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="52"/>
       <c r="B7" s="12">
         <v>46054</v>
       </c>
-      <c r="C7" s="15">
-        <v>80</v>
+      <c r="C7" s="16">
+        <v>184</v>
       </c>
       <c r="D7" s="6">
         <v>312</v>
@@ -4903,10 +4844,10 @@
       <c r="G7" s="6">
         <v>75</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <v>750</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="26">
         <v>150</v>
       </c>
       <c r="J7" s="6">
@@ -4921,8 +4862,8 @@
       <c r="M7" s="6">
         <v>53</v>
       </c>
-      <c r="N7" s="53"/>
-      <c r="O7" s="53"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
       <c r="P7" s="6">
         <v>22</v>
       </c>
@@ -4930,13 +4871,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8" s="42"/>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="52"/>
       <c r="B8" s="12">
         <v>46082</v>
       </c>
-      <c r="C8" s="15">
-        <v>70</v>
+      <c r="C8" s="16">
+        <v>110</v>
       </c>
       <c r="D8" s="6">
         <v>318</v>
@@ -4950,14 +4891,14 @@
       <c r="G8" s="6">
         <v>80</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="15">
         <v>500</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="26">
         <v>350</v>
       </c>
       <c r="J8" s="6">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="K8" s="6">
         <v>80</v>
@@ -4968,8 +4909,8 @@
       <c r="M8" s="6">
         <v>70</v>
       </c>
-      <c r="N8" s="53"/>
-      <c r="O8" s="53"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="66"/>
       <c r="P8" s="6">
         <v>8</v>
       </c>
@@ -4977,13 +4918,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9" s="42"/>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="52"/>
       <c r="B9" s="12">
         <v>46113</v>
       </c>
-      <c r="C9" s="15">
-        <v>55</v>
+      <c r="C9" s="16">
+        <v>142</v>
       </c>
       <c r="D9" s="6">
         <v>261</v>
@@ -4997,14 +4938,14 @@
       <c r="G9" s="6">
         <v>80</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <v>500</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="26">
         <v>220</v>
       </c>
       <c r="J9" s="6">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="K9" s="6">
         <v>110</v>
@@ -5015,8 +4956,8 @@
       <c r="M9" s="6">
         <v>33</v>
       </c>
-      <c r="N9" s="53"/>
-      <c r="O9" s="53"/>
+      <c r="N9" s="66"/>
+      <c r="O9" s="66"/>
       <c r="P9" s="6">
         <v>13</v>
       </c>
@@ -5024,13 +4965,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A10" s="42"/>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="52"/>
       <c r="B10" s="12">
         <v>46143</v>
       </c>
-      <c r="C10" s="15">
-        <v>60</v>
+      <c r="C10" s="16">
+        <v>160</v>
       </c>
       <c r="D10" s="6">
         <v>210</v>
@@ -5044,14 +4985,14 @@
       <c r="G10" s="6">
         <v>60</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="15">
         <v>500</v>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="26">
         <v>80</v>
       </c>
       <c r="J10" s="6">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K10" s="6">
         <v>110</v>
@@ -5062,8 +5003,8 @@
       <c r="M10" s="6">
         <v>40</v>
       </c>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
       <c r="P10" s="6">
         <v>0</v>
       </c>
@@ -5071,13 +5012,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A11" s="42"/>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="52"/>
       <c r="B11" s="12">
         <v>46174</v>
       </c>
-      <c r="C11" s="15">
-        <v>86</v>
+      <c r="C11" s="16">
+        <v>219</v>
       </c>
       <c r="D11" s="6">
         <v>329</v>
@@ -5091,10 +5032,10 @@
       <c r="G11" s="6">
         <v>60</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <v>500</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="26">
         <v>90</v>
       </c>
       <c r="J11" s="6">
@@ -5109,8 +5050,8 @@
       <c r="M11" s="6">
         <v>0</v>
       </c>
-      <c r="N11" s="53"/>
-      <c r="O11" s="53"/>
+      <c r="N11" s="66"/>
+      <c r="O11" s="66"/>
       <c r="P11" s="6">
         <v>0</v>
       </c>
@@ -5118,13 +5059,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="42"/>
+    <row r="12" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="52"/>
       <c r="B12" s="10">
         <v>46204</v>
       </c>
       <c r="C12" s="18">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="D12" s="7">
         <v>244</v>
@@ -5138,14 +5079,14 @@
       <c r="G12" s="7">
         <v>70</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="17">
         <v>500</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="27">
         <v>120</v>
       </c>
       <c r="J12" s="6">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K12" s="7">
         <v>120</v>
@@ -5156,8 +5097,8 @@
       <c r="M12" s="7">
         <v>0</v>
       </c>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
+      <c r="N12" s="67"/>
+      <c r="O12" s="67"/>
       <c r="P12" s="7">
         <v>0</v>
       </c>
@@ -5165,81 +5106,81 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="65" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="43"/>
-      <c r="B13" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="27">
-        <f t="shared" ref="C13:Q13" si="0">+C4+C5+C6+C7+C8+C9+C10+C11+C12</f>
-        <v>905</v>
-      </c>
-      <c r="D13" s="28">
-        <f t="shared" si="0"/>
+    <row r="13" spans="1:17" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="53"/>
+      <c r="B13" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="25">
+        <f t="shared" ref="C13" si="0">+C4+C5+C6+C7+C8+C9+C10+C11+C12</f>
+        <v>1514</v>
+      </c>
+      <c r="D13" s="23">
+        <f t="shared" ref="D13:Q13" si="1">+D4+D5+D6+D7+D8+D9+D10+D11+D12</f>
         <v>2357</v>
       </c>
-      <c r="E13" s="28">
-        <f t="shared" si="0"/>
+      <c r="E13" s="23">
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="F13" s="28">
-        <f t="shared" si="0"/>
+      <c r="F13" s="23">
+        <f t="shared" si="1"/>
         <v>342</v>
       </c>
-      <c r="G13" s="28">
-        <f t="shared" si="0"/>
+      <c r="G13" s="23">
+        <f t="shared" si="1"/>
         <v>675</v>
       </c>
-      <c r="H13" s="29">
-        <f t="shared" si="0"/>
+      <c r="H13" s="24">
+        <f t="shared" si="1"/>
         <v>6250</v>
       </c>
-      <c r="I13" s="38">
-        <f t="shared" si="0"/>
+      <c r="I13" s="32">
+        <f t="shared" si="1"/>
         <v>1450</v>
       </c>
-      <c r="J13" s="34">
-        <f t="shared" si="0"/>
-        <v>522</v>
-      </c>
-      <c r="K13" s="28">
-        <f t="shared" si="0"/>
+      <c r="J13" s="29">
+        <f t="shared" si="1"/>
+        <v>717</v>
+      </c>
+      <c r="K13" s="23">
+        <f t="shared" si="1"/>
         <v>735</v>
       </c>
-      <c r="L13" s="28">
-        <f t="shared" si="0"/>
+      <c r="L13" s="23">
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="M13" s="28">
-        <f t="shared" si="0"/>
+      <c r="M13" s="23">
+        <f t="shared" si="1"/>
         <v>241</v>
       </c>
-      <c r="N13" s="28">
-        <f t="shared" si="0"/>
+      <c r="N13" s="23">
+        <f t="shared" si="1"/>
         <v>2500</v>
       </c>
-      <c r="O13" s="28">
-        <f t="shared" si="0"/>
+      <c r="O13" s="23">
+        <f t="shared" si="1"/>
         <v>2000</v>
       </c>
-      <c r="P13" s="28">
-        <f t="shared" si="0"/>
+      <c r="P13" s="23">
+        <f t="shared" si="1"/>
         <v>81</v>
       </c>
-      <c r="Q13" s="28">
-        <f t="shared" si="0"/>
+      <c r="Q13" s="23">
+        <f t="shared" si="1"/>
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A14" s="40" t="s">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="50" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="12">
         <v>45962</v>
       </c>
-      <c r="C14" s="15">
-        <v>40</v>
+      <c r="C14" s="21">
+        <v>89</v>
       </c>
       <c r="D14" s="6">
         <v>137</v>
@@ -5253,11 +5194,11 @@
       <c r="G14" s="6">
         <v>25</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <f>529+630</f>
         <v>1159</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="16">
         <v>200</v>
       </c>
       <c r="J14" s="6">
@@ -5272,10 +5213,10 @@
       <c r="M14" s="6">
         <v>20</v>
       </c>
-      <c r="N14" s="52">
+      <c r="N14" s="65">
         <v>3000</v>
       </c>
-      <c r="O14" s="52">
+      <c r="O14" s="65">
         <v>2000</v>
       </c>
       <c r="P14" s="6">
@@ -5285,13 +5226,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A15" s="40"/>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="50"/>
       <c r="B15" s="12">
         <v>45992</v>
       </c>
-      <c r="C15" s="15">
-        <v>20</v>
+      <c r="C15" s="16">
+        <v>35</v>
       </c>
       <c r="D15" s="6">
         <v>152</v>
@@ -5305,11 +5246,11 @@
       <c r="G15" s="6">
         <v>19</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="15">
         <f>459+370</f>
         <v>829</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="16">
         <v>160</v>
       </c>
       <c r="J15" s="6">
@@ -5324,8 +5265,8 @@
       <c r="M15" s="6">
         <v>13</v>
       </c>
-      <c r="N15" s="53"/>
-      <c r="O15" s="53"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
       <c r="P15" s="6">
         <v>2</v>
       </c>
@@ -5333,13 +5274,13 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A16" s="40"/>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="50"/>
       <c r="B16" s="12">
         <v>46023</v>
       </c>
-      <c r="C16" s="15">
-        <v>22</v>
+      <c r="C16" s="16">
+        <v>142</v>
       </c>
       <c r="D16" s="6">
         <v>284</v>
@@ -5353,10 +5294,10 @@
       <c r="G16" s="6">
         <v>0</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="15">
         <v>12</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="16">
         <v>140</v>
       </c>
       <c r="J16" s="6">
@@ -5371,8 +5312,8 @@
       <c r="M16" s="6">
         <v>10</v>
       </c>
-      <c r="N16" s="53"/>
-      <c r="O16" s="53"/>
+      <c r="N16" s="66"/>
+      <c r="O16" s="66"/>
       <c r="P16" s="6">
         <v>0</v>
       </c>
@@ -5380,13 +5321,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A17" s="40"/>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="50"/>
       <c r="B17" s="12">
         <v>46054</v>
       </c>
-      <c r="C17" s="15">
-        <v>24</v>
+      <c r="C17" s="16">
+        <v>124</v>
       </c>
       <c r="D17" s="6">
         <v>282</v>
@@ -5400,10 +5341,10 @@
       <c r="G17" s="6">
         <v>13</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="15">
         <v>190</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="16">
         <v>150</v>
       </c>
       <c r="J17" s="6">
@@ -5418,8 +5359,8 @@
       <c r="M17" s="6">
         <v>20</v>
       </c>
-      <c r="N17" s="53"/>
-      <c r="O17" s="53"/>
+      <c r="N17" s="66"/>
+      <c r="O17" s="66"/>
       <c r="P17" s="6">
         <v>1</v>
       </c>
@@ -5427,12 +5368,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A18" s="40"/>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" s="50"/>
       <c r="B18" s="12">
         <v>46082</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="16">
         <v>104</v>
       </c>
       <c r="D18" s="6">
@@ -5447,10 +5388,10 @@
       <c r="G18" s="6">
         <v>3</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="15">
         <v>30</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="16">
         <v>150</v>
       </c>
       <c r="J18" s="6">
@@ -5465,8 +5406,8 @@
       <c r="M18" s="6">
         <v>16</v>
       </c>
-      <c r="N18" s="53"/>
-      <c r="O18" s="53"/>
+      <c r="N18" s="66"/>
+      <c r="O18" s="66"/>
       <c r="P18" s="6">
         <v>2</v>
       </c>
@@ -5474,13 +5415,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A19" s="40"/>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" s="50"/>
       <c r="B19" s="12">
         <v>46113</v>
       </c>
-      <c r="C19" s="15">
-        <v>110</v>
+      <c r="C19" s="16">
+        <v>251</v>
       </c>
       <c r="D19" s="6">
         <v>360</v>
@@ -5494,10 +5435,10 @@
       <c r="G19" s="6">
         <v>0</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="15">
         <v>5</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="16">
         <v>80</v>
       </c>
       <c r="J19" s="6">
@@ -5512,8 +5453,8 @@
       <c r="M19" s="6">
         <v>12</v>
       </c>
-      <c r="N19" s="53"/>
-      <c r="O19" s="53"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="66"/>
       <c r="P19" s="6">
         <v>3</v>
       </c>
@@ -5521,13 +5462,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A20" s="40"/>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="50"/>
       <c r="B20" s="12">
         <v>46143</v>
       </c>
-      <c r="C20" s="15">
-        <v>40</v>
+      <c r="C20" s="16">
+        <v>298</v>
       </c>
       <c r="D20" s="6">
         <v>439</v>
@@ -5541,10 +5482,10 @@
       <c r="G20" s="6">
         <v>0</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="15">
         <v>35</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="16">
         <v>120</v>
       </c>
       <c r="J20" s="6">
@@ -5559,8 +5500,8 @@
       <c r="M20" s="6">
         <v>10</v>
       </c>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="66"/>
       <c r="P20" s="6">
         <v>0</v>
       </c>
@@ -5568,13 +5509,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A21" s="40"/>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" s="50"/>
       <c r="B21" s="12">
         <v>46174</v>
       </c>
-      <c r="C21" s="15">
-        <v>20</v>
+      <c r="C21" s="16">
+        <v>268</v>
       </c>
       <c r="D21" s="6">
         <v>390</v>
@@ -5588,10 +5529,10 @@
       <c r="G21" s="6">
         <v>0</v>
       </c>
-      <c r="H21" s="16">
-        <v>0</v>
-      </c>
-      <c r="I21" s="17">
+      <c r="H21" s="15">
+        <v>0</v>
+      </c>
+      <c r="I21" s="16">
         <v>140</v>
       </c>
       <c r="J21" s="6">
@@ -5606,8 +5547,8 @@
       <c r="M21" s="6">
         <v>20</v>
       </c>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="66"/>
       <c r="P21" s="6">
         <v>0</v>
       </c>
@@ -5615,13 +5556,13 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="40"/>
+    <row r="22" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="50"/>
       <c r="B22" s="10">
         <v>46204</v>
       </c>
       <c r="C22" s="18">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="D22" s="7">
         <v>246</v>
@@ -5629,16 +5570,16 @@
       <c r="E22" s="7">
         <v>2</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="33">
         <v>4</v>
       </c>
       <c r="G22" s="7">
         <v>0</v>
       </c>
-      <c r="H22" s="19">
-        <v>0</v>
-      </c>
-      <c r="I22" s="17">
+      <c r="H22" s="17">
+        <v>0</v>
+      </c>
+      <c r="I22" s="16">
         <v>150</v>
       </c>
       <c r="J22" s="6">
@@ -5653,8 +5594,8 @@
       <c r="M22" s="7">
         <v>6</v>
       </c>
-      <c r="N22" s="54"/>
-      <c r="O22" s="54"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="67"/>
       <c r="P22" s="7">
         <v>0</v>
       </c>
@@ -5662,80 +5603,80 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="65" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="41"/>
-      <c r="B23" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="27">
-        <f t="shared" ref="C23:H23" si="1">+C14+C15+C16+C17+C18+C19+C20+C21+C22</f>
-        <v>398</v>
-      </c>
-      <c r="D23" s="28">
-        <f t="shared" si="1"/>
+    <row r="23" spans="1:17" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="51"/>
+      <c r="B23" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="25">
+        <f t="shared" ref="C23" si="2">+C14+C15+C16+C17+C18+C19+C20+C21+C22</f>
+        <v>1529</v>
+      </c>
+      <c r="D23" s="23">
+        <f t="shared" ref="D23:H23" si="3">+D14+D15+D16+D17+D18+D19+D20+D21+D22</f>
         <v>2514</v>
       </c>
-      <c r="E23" s="28">
-        <f t="shared" si="1"/>
+      <c r="E23" s="23">
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
-      <c r="F23" s="28">
-        <f t="shared" si="1"/>
+      <c r="F23" s="23">
+        <f t="shared" si="3"/>
         <v>174</v>
       </c>
-      <c r="G23" s="28">
-        <f t="shared" si="1"/>
+      <c r="G23" s="23">
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="H23" s="29">
-        <f t="shared" si="1"/>
+      <c r="H23" s="24">
+        <f t="shared" si="3"/>
         <v>2260</v>
       </c>
-      <c r="I23" s="30">
-        <f t="shared" ref="I23:J23" si="2">+I14+I15+I16+I17+I18+I19+I20+I21+I22</f>
+      <c r="I23" s="25">
+        <f t="shared" ref="I23:J23" si="4">+I14+I15+I16+I17+I18+I19+I20+I21+I22</f>
         <v>1290</v>
       </c>
-      <c r="J23" s="28">
-        <f t="shared" si="2"/>
+      <c r="J23" s="23">
+        <f t="shared" si="4"/>
         <v>642</v>
       </c>
-      <c r="K23" s="28">
-        <f t="shared" ref="K23:Q23" si="3">+K14+K15+K16+K17+K18+K19+K20+K21+K22</f>
+      <c r="K23" s="23">
+        <f t="shared" ref="K23:Q23" si="5">+K14+K15+K16+K17+K18+K19+K20+K21+K22</f>
         <v>316</v>
       </c>
-      <c r="L23" s="28">
-        <f t="shared" si="3"/>
+      <c r="L23" s="23">
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="M23" s="28">
-        <f t="shared" si="3"/>
+      <c r="M23" s="23">
+        <f t="shared" si="5"/>
         <v>127</v>
       </c>
-      <c r="N23" s="28">
-        <f t="shared" si="3"/>
+      <c r="N23" s="23">
+        <f t="shared" si="5"/>
         <v>3000</v>
       </c>
-      <c r="O23" s="28">
-        <f t="shared" si="3"/>
+      <c r="O23" s="23">
+        <f t="shared" si="5"/>
         <v>2000</v>
       </c>
-      <c r="P23" s="28">
-        <f t="shared" si="3"/>
+      <c r="P23" s="23">
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="Q23" s="28">
-        <f t="shared" si="3"/>
+      <c r="Q23" s="23">
+        <f t="shared" si="5"/>
         <v>223</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A24" s="40" t="s">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" s="50" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="12">
         <v>45962</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="21">
         <v>48</v>
       </c>
       <c r="D24" s="6">
@@ -5750,10 +5691,10 @@
       <c r="G24" s="6">
         <v>0</v>
       </c>
-      <c r="H24" s="16">
-        <v>0</v>
-      </c>
-      <c r="I24" s="31">
+      <c r="H24" s="15">
+        <v>0</v>
+      </c>
+      <c r="I24" s="26">
         <v>90</v>
       </c>
       <c r="J24" s="6">
@@ -5768,10 +5709,10 @@
       <c r="M24" s="6">
         <v>27</v>
       </c>
-      <c r="N24" s="52">
+      <c r="N24" s="65">
         <v>2500</v>
       </c>
-      <c r="O24" s="52">
+      <c r="O24" s="65">
         <v>2000</v>
       </c>
       <c r="P24" s="6">
@@ -5781,12 +5722,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A25" s="40"/>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="50"/>
       <c r="B25" s="12">
         <v>45992</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="16">
         <v>28</v>
       </c>
       <c r="D25" s="6">
@@ -5801,10 +5742,10 @@
       <c r="G25" s="6">
         <v>0</v>
       </c>
-      <c r="H25" s="16">
-        <v>0</v>
-      </c>
-      <c r="I25" s="31">
+      <c r="H25" s="15">
+        <v>0</v>
+      </c>
+      <c r="I25" s="26">
         <v>150</v>
       </c>
       <c r="J25" s="6">
@@ -5819,8 +5760,8 @@
       <c r="M25" s="6">
         <v>0</v>
       </c>
-      <c r="N25" s="53"/>
-      <c r="O25" s="53"/>
+      <c r="N25" s="66"/>
+      <c r="O25" s="66"/>
       <c r="P25" s="6">
         <v>0</v>
       </c>
@@ -5828,12 +5769,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A26" s="40"/>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" s="50"/>
       <c r="B26" s="12">
         <v>46023</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="16">
         <v>30</v>
       </c>
       <c r="D26" s="6">
@@ -5848,10 +5789,10 @@
       <c r="G26" s="6">
         <v>0</v>
       </c>
-      <c r="H26" s="16">
-        <v>0</v>
-      </c>
-      <c r="I26" s="31">
+      <c r="H26" s="15">
+        <v>0</v>
+      </c>
+      <c r="I26" s="26">
         <v>200</v>
       </c>
       <c r="J26" s="6">
@@ -5866,8 +5807,8 @@
       <c r="M26" s="6">
         <v>0</v>
       </c>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
+      <c r="N26" s="66"/>
+      <c r="O26" s="66"/>
       <c r="P26" s="6">
         <v>2</v>
       </c>
@@ -5875,13 +5816,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A27" s="40"/>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27" s="50"/>
       <c r="B27" s="12">
         <v>46054</v>
       </c>
-      <c r="C27" s="15">
-        <v>32</v>
+      <c r="C27" s="16">
+        <v>72</v>
       </c>
       <c r="D27" s="6">
         <v>102</v>
@@ -5895,10 +5836,10 @@
       <c r="G27" s="6">
         <v>0</v>
       </c>
-      <c r="H27" s="16">
-        <v>0</v>
-      </c>
-      <c r="I27" s="31">
+      <c r="H27" s="15">
+        <v>0</v>
+      </c>
+      <c r="I27" s="26">
         <v>150</v>
       </c>
       <c r="J27" s="6">
@@ -5913,8 +5854,8 @@
       <c r="M27" s="6">
         <v>0</v>
       </c>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
+      <c r="N27" s="66"/>
+      <c r="O27" s="66"/>
       <c r="P27" s="6">
         <v>4</v>
       </c>
@@ -5922,12 +5863,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A28" s="40"/>
+    <row r="28" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="50"/>
       <c r="B28" s="12">
         <v>46082</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="39">
         <v>102</v>
       </c>
       <c r="D28" s="6">
@@ -5942,10 +5883,10 @@
       <c r="G28" s="6">
         <v>10</v>
       </c>
-      <c r="H28" s="16">
-        <v>0</v>
-      </c>
-      <c r="I28" s="31">
+      <c r="H28" s="15">
+        <v>0</v>
+      </c>
+      <c r="I28" s="26">
         <v>120</v>
       </c>
       <c r="J28" s="6">
@@ -5960,8 +5901,8 @@
       <c r="M28" s="6">
         <v>1</v>
       </c>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="66"/>
       <c r="P28" s="6">
         <v>1</v>
       </c>
@@ -5969,12 +5910,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A29" s="40"/>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" s="50"/>
       <c r="B29" s="12">
         <v>46113</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="16">
         <v>119</v>
       </c>
       <c r="D29" s="6">
@@ -5989,10 +5930,10 @@
       <c r="G29" s="6">
         <v>0</v>
       </c>
-      <c r="H29" s="16">
-        <v>0</v>
-      </c>
-      <c r="I29" s="31">
+      <c r="H29" s="15">
+        <v>0</v>
+      </c>
+      <c r="I29" s="26">
         <v>140</v>
       </c>
       <c r="J29" s="6">
@@ -6007,8 +5948,8 @@
       <c r="M29" s="6">
         <v>16</v>
       </c>
-      <c r="N29" s="53"/>
-      <c r="O29" s="53"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="66"/>
       <c r="P29" s="6">
         <v>5</v>
       </c>
@@ -6016,13 +5957,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A30" s="40"/>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A30" s="50"/>
       <c r="B30" s="12">
         <v>46143</v>
       </c>
-      <c r="C30" s="15">
-        <v>48</v>
+      <c r="C30" s="16">
+        <v>168</v>
       </c>
       <c r="D30" s="6">
         <v>204</v>
@@ -6036,10 +5977,10 @@
       <c r="G30" s="6">
         <v>30</v>
       </c>
-      <c r="H30" s="16">
-        <v>0</v>
-      </c>
-      <c r="I30" s="31">
+      <c r="H30" s="15">
+        <v>0</v>
+      </c>
+      <c r="I30" s="26">
         <v>180</v>
       </c>
       <c r="J30" s="6">
@@ -6054,8 +5995,8 @@
       <c r="M30" s="6">
         <v>3</v>
       </c>
-      <c r="N30" s="53"/>
-      <c r="O30" s="53"/>
+      <c r="N30" s="66"/>
+      <c r="O30" s="66"/>
       <c r="P30" s="6">
         <v>0</v>
       </c>
@@ -6063,13 +6004,13 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A31" s="40"/>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" s="50"/>
       <c r="B31" s="12">
         <v>46174</v>
       </c>
-      <c r="C31" s="15">
-        <v>26</v>
+      <c r="C31" s="16">
+        <v>165</v>
       </c>
       <c r="D31" s="6">
         <v>215</v>
@@ -6083,10 +6024,10 @@
       <c r="G31" s="6">
         <v>0</v>
       </c>
-      <c r="H31" s="16">
-        <v>0</v>
-      </c>
-      <c r="I31" s="31">
+      <c r="H31" s="15">
+        <v>0</v>
+      </c>
+      <c r="I31" s="26">
         <v>40</v>
       </c>
       <c r="J31" s="6">
@@ -6101,8 +6042,8 @@
       <c r="M31" s="6">
         <v>0</v>
       </c>
-      <c r="N31" s="53"/>
-      <c r="O31" s="53"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="66"/>
       <c r="P31" s="6">
         <v>0</v>
       </c>
@@ -6110,13 +6051,13 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="40"/>
+    <row r="32" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="50"/>
       <c r="B32" s="10">
         <v>46204</v>
       </c>
-      <c r="C32" s="18">
-        <v>28</v>
+      <c r="C32" s="39">
+        <v>188</v>
       </c>
       <c r="D32" s="7">
         <v>232</v>
@@ -6130,10 +6071,10 @@
       <c r="G32" s="7">
         <v>0</v>
       </c>
-      <c r="H32" s="19">
-        <v>0</v>
-      </c>
-      <c r="I32" s="32">
+      <c r="H32" s="17">
+        <v>0</v>
+      </c>
+      <c r="I32" s="27">
         <v>110</v>
       </c>
       <c r="J32" s="7">
@@ -6148,8 +6089,8 @@
       <c r="M32" s="7">
         <v>0</v>
       </c>
-      <c r="N32" s="54"/>
-      <c r="O32" s="54"/>
+      <c r="N32" s="67"/>
+      <c r="O32" s="67"/>
       <c r="P32" s="7">
         <v>1</v>
       </c>
@@ -6157,81 +6098,81 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="65" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="41"/>
-      <c r="B33" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="27">
-        <f t="shared" ref="C33:Q33" si="4">+C24+C25+C26+C27+C28+C29+C30+C31+C32</f>
-        <v>461</v>
-      </c>
-      <c r="D33" s="28">
-        <f t="shared" si="4"/>
+    <row r="33" spans="1:17" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="51"/>
+      <c r="B33" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="25">
+        <f t="shared" ref="C33" si="6">+C24+C25+C26+C27+C28+C29+C30+C31+C32</f>
+        <v>920</v>
+      </c>
+      <c r="D33" s="23">
+        <f t="shared" ref="D33:Q33" si="7">+D24+D25+D26+D27+D28+D29+D30+D31+D32</f>
         <v>1127</v>
       </c>
-      <c r="E33" s="28">
-        <f t="shared" si="4"/>
+      <c r="E33" s="23">
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
-      <c r="F33" s="28">
-        <f t="shared" si="4"/>
+      <c r="F33" s="23">
+        <f t="shared" si="7"/>
         <v>219</v>
       </c>
-      <c r="G33" s="28">
-        <f t="shared" si="4"/>
+      <c r="G33" s="23">
+        <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="H33" s="29">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="30">
-        <f t="shared" si="4"/>
+      <c r="H33" s="24">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="25">
+        <f t="shared" si="7"/>
         <v>1180</v>
       </c>
-      <c r="J33" s="28">
-        <f t="shared" si="4"/>
+      <c r="J33" s="23">
+        <f t="shared" si="7"/>
         <v>480</v>
       </c>
-      <c r="K33" s="28">
-        <f t="shared" si="4"/>
+      <c r="K33" s="23">
+        <f t="shared" si="7"/>
         <v>615</v>
       </c>
-      <c r="L33" s="28">
-        <f t="shared" si="4"/>
+      <c r="L33" s="23">
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="M33" s="28">
-        <f t="shared" si="4"/>
+      <c r="M33" s="23">
+        <f t="shared" si="7"/>
         <v>47</v>
       </c>
-      <c r="N33" s="28">
-        <f t="shared" si="4"/>
+      <c r="N33" s="23">
+        <f t="shared" si="7"/>
         <v>2500</v>
       </c>
-      <c r="O33" s="28">
-        <f t="shared" si="4"/>
+      <c r="O33" s="23">
+        <f t="shared" si="7"/>
         <v>2000</v>
       </c>
-      <c r="P33" s="28">
-        <f t="shared" si="4"/>
+      <c r="P33" s="23">
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="Q33" s="28">
-        <f t="shared" si="4"/>
+      <c r="Q33" s="23">
+        <f t="shared" si="7"/>
         <v>187</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="40" t="s">
+    <row r="34" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="50" t="s">
         <v>24</v>
       </c>
       <c r="B34" s="13">
         <v>45962</v>
       </c>
-      <c r="C34" s="35">
-        <v>30</v>
+      <c r="C34" s="42">
+        <v>109</v>
       </c>
       <c r="D34" s="7">
         <v>180</v>
@@ -6245,43 +6186,43 @@
       <c r="G34" s="7">
         <v>0</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="17">
         <v>220</v>
       </c>
-      <c r="I34" s="36">
+      <c r="I34" s="30">
         <v>135</v>
       </c>
-      <c r="J34" s="39">
+      <c r="J34" s="33">
         <v>40</v>
       </c>
-      <c r="K34" s="37">
+      <c r="K34" s="31">
         <v>70</v>
       </c>
-      <c r="L34" s="39">
+      <c r="L34" s="33">
         <v>3</v>
       </c>
-      <c r="M34" s="39">
-        <v>0</v>
-      </c>
-      <c r="N34" s="52">
+      <c r="M34" s="33">
+        <v>0</v>
+      </c>
+      <c r="N34" s="65">
         <v>2000</v>
       </c>
-      <c r="O34" s="52">
+      <c r="O34" s="65">
         <v>2000</v>
       </c>
-      <c r="P34" s="39">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="39">
+      <c r="P34" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="33">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A35" s="40"/>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A35" s="50"/>
       <c r="B35" s="12">
         <v>45992</v>
       </c>
-      <c r="C35" s="21">
+      <c r="C35" s="43">
         <v>45</v>
       </c>
       <c r="D35" s="6">
@@ -6296,11 +6237,11 @@
       <c r="G35" s="6">
         <v>30</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="15">
         <f>136+780+358</f>
         <v>1274</v>
       </c>
-      <c r="I35" s="17">
+      <c r="I35" s="16">
         <v>200</v>
       </c>
       <c r="J35" s="6">
@@ -6316,8 +6257,8 @@
         <f>25+49</f>
         <v>74</v>
       </c>
-      <c r="N35" s="53"/>
-      <c r="O35" s="53"/>
+      <c r="N35" s="66"/>
+      <c r="O35" s="66"/>
       <c r="P35" s="6">
         <v>5</v>
       </c>
@@ -6325,13 +6266,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A36" s="40"/>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A36" s="50"/>
       <c r="B36" s="12">
         <v>46023</v>
       </c>
-      <c r="C36" s="21">
-        <v>62</v>
+      <c r="C36" s="43">
+        <v>94</v>
       </c>
       <c r="D36" s="6">
         <v>116</v>
@@ -6345,10 +6286,10 @@
       <c r="G36" s="6">
         <v>0</v>
       </c>
-      <c r="H36" s="16">
-        <v>0</v>
-      </c>
-      <c r="I36" s="17">
+      <c r="H36" s="15">
+        <v>0</v>
+      </c>
+      <c r="I36" s="16">
         <v>190</v>
       </c>
       <c r="J36" s="6">
@@ -6363,8 +6304,8 @@
       <c r="M36" s="6">
         <v>0</v>
       </c>
-      <c r="N36" s="53"/>
-      <c r="O36" s="53"/>
+      <c r="N36" s="66"/>
+      <c r="O36" s="66"/>
       <c r="P36" s="6">
         <v>2</v>
       </c>
@@ -6372,13 +6313,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A37" s="40"/>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A37" s="50"/>
       <c r="B37" s="12">
         <v>46054</v>
       </c>
-      <c r="C37" s="21">
-        <v>43</v>
+      <c r="C37" s="43">
+        <v>113</v>
       </c>
       <c r="D37" s="6">
         <v>166</v>
@@ -6392,11 +6333,11 @@
       <c r="G37" s="6">
         <v>0</v>
       </c>
-      <c r="H37" s="16">
+      <c r="H37" s="15">
         <f>264+70</f>
         <v>334</v>
       </c>
-      <c r="I37" s="31">
+      <c r="I37" s="26">
         <v>180</v>
       </c>
       <c r="J37" s="6">
@@ -6411,8 +6352,8 @@
       <c r="M37" s="6">
         <v>0</v>
       </c>
-      <c r="N37" s="53"/>
-      <c r="O37" s="53"/>
+      <c r="N37" s="66"/>
+      <c r="O37" s="66"/>
       <c r="P37" s="6">
         <v>2</v>
       </c>
@@ -6420,13 +6361,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A38" s="40"/>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38" s="50"/>
       <c r="B38" s="12">
         <v>46082</v>
       </c>
-      <c r="C38" s="21">
-        <v>55</v>
+      <c r="C38" s="43">
+        <v>255</v>
       </c>
       <c r="D38" s="6">
         <f>374-67</f>
@@ -6441,11 +6382,11 @@
       <c r="G38" s="6">
         <v>220</v>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="15">
         <f>450+72</f>
         <v>522</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="26">
         <v>180</v>
       </c>
       <c r="J38" s="6">
@@ -6460,8 +6401,8 @@
       <c r="M38" s="6">
         <v>11</v>
       </c>
-      <c r="N38" s="53"/>
-      <c r="O38" s="53"/>
+      <c r="N38" s="66"/>
+      <c r="O38" s="66"/>
       <c r="P38" s="6">
         <v>7</v>
       </c>
@@ -6469,13 +6410,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A39" s="40"/>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A39" s="50"/>
       <c r="B39" s="12">
         <v>46113</v>
       </c>
-      <c r="C39" s="15">
-        <v>60</v>
+      <c r="C39" s="16">
+        <v>160</v>
       </c>
       <c r="D39" s="6">
         <v>384</v>
@@ -6489,10 +6430,10 @@
       <c r="G39" s="6">
         <v>100</v>
       </c>
-      <c r="H39" s="16">
+      <c r="H39" s="15">
         <v>630</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="26">
         <v>160</v>
       </c>
       <c r="J39" s="6">
@@ -6507,8 +6448,8 @@
       <c r="M39" s="6">
         <v>180</v>
       </c>
-      <c r="N39" s="53"/>
-      <c r="O39" s="53"/>
+      <c r="N39" s="66"/>
+      <c r="O39" s="66"/>
       <c r="P39" s="6">
         <v>1</v>
       </c>
@@ -6516,13 +6457,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A40" s="40"/>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A40" s="50"/>
       <c r="B40" s="12">
         <v>46143</v>
       </c>
-      <c r="C40" s="15">
-        <v>82</v>
+      <c r="C40" s="16">
+        <v>282</v>
       </c>
       <c r="D40" s="6">
         <v>435</v>
@@ -6536,10 +6477,10 @@
       <c r="G40" s="6">
         <v>0</v>
       </c>
-      <c r="H40" s="16">
+      <c r="H40" s="15">
         <v>504</v>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="26">
         <v>150</v>
       </c>
       <c r="J40" s="6">
@@ -6554,8 +6495,8 @@
       <c r="M40" s="6">
         <v>60</v>
       </c>
-      <c r="N40" s="53"/>
-      <c r="O40" s="53"/>
+      <c r="N40" s="66"/>
+      <c r="O40" s="66"/>
       <c r="P40" s="6">
         <v>5</v>
       </c>
@@ -6563,13 +6504,13 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A41" s="40"/>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A41" s="50"/>
       <c r="B41" s="12">
         <v>46174</v>
       </c>
-      <c r="C41" s="15">
-        <v>87</v>
+      <c r="C41" s="16">
+        <v>187</v>
       </c>
       <c r="D41" s="6">
         <v>334</v>
@@ -6583,10 +6524,10 @@
       <c r="G41" s="6">
         <v>0</v>
       </c>
-      <c r="H41" s="16">
-        <v>0</v>
-      </c>
-      <c r="I41" s="31">
+      <c r="H41" s="15">
+        <v>0</v>
+      </c>
+      <c r="I41" s="26">
         <v>140</v>
       </c>
       <c r="J41" s="6">
@@ -6601,8 +6542,8 @@
       <c r="M41" s="6">
         <v>0</v>
       </c>
-      <c r="N41" s="53"/>
-      <c r="O41" s="53"/>
+      <c r="N41" s="66"/>
+      <c r="O41" s="66"/>
       <c r="P41" s="6">
         <v>0</v>
       </c>
@@ -6610,12 +6551,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="40"/>
+    <row r="42" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="50"/>
       <c r="B42" s="10">
         <v>46204</v>
       </c>
-      <c r="C42" s="18">
+      <c r="C42" s="39">
         <v>110</v>
       </c>
       <c r="D42" s="7">
@@ -6630,10 +6571,10 @@
       <c r="G42" s="7">
         <v>0</v>
       </c>
-      <c r="H42" s="19">
-        <v>0</v>
-      </c>
-      <c r="I42" s="32">
+      <c r="H42" s="17">
+        <v>0</v>
+      </c>
+      <c r="I42" s="27">
         <v>140</v>
       </c>
       <c r="J42" s="7">
@@ -6648,8 +6589,8 @@
       <c r="M42" s="7">
         <v>0</v>
       </c>
-      <c r="N42" s="54"/>
-      <c r="O42" s="54"/>
+      <c r="N42" s="67"/>
+      <c r="O42" s="67"/>
       <c r="P42" s="7">
         <v>0</v>
       </c>
@@ -6657,81 +6598,81 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="65" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="41"/>
-      <c r="B43" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C43" s="27">
-        <f t="shared" ref="C43:Q43" si="5">+C34+C35+C36+C37+C38+C39+C40+C41+C42</f>
-        <v>574</v>
-      </c>
-      <c r="D43" s="28">
-        <f t="shared" si="5"/>
+    <row r="43" spans="1:17" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="51"/>
+      <c r="B43" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="25">
+        <f t="shared" ref="C43" si="8">+C34+C35+C36+C37+C38+C39+C40+C41+C42</f>
+        <v>1355</v>
+      </c>
+      <c r="D43" s="23">
+        <f t="shared" ref="D43:Q43" si="9">+D34+D35+D36+D37+D38+D39+D40+D41+D42</f>
         <v>2255</v>
       </c>
-      <c r="E43" s="28">
-        <f t="shared" si="5"/>
+      <c r="E43" s="23">
+        <f t="shared" si="9"/>
         <v>74</v>
       </c>
-      <c r="F43" s="28">
-        <f t="shared" si="5"/>
+      <c r="F43" s="23">
+        <f t="shared" si="9"/>
         <v>295</v>
       </c>
-      <c r="G43" s="28">
-        <f t="shared" si="5"/>
+      <c r="G43" s="23">
+        <f t="shared" si="9"/>
         <v>350</v>
       </c>
-      <c r="H43" s="29">
-        <f t="shared" si="5"/>
+      <c r="H43" s="24">
+        <f t="shared" si="9"/>
         <v>3484</v>
       </c>
-      <c r="I43" s="30">
-        <f t="shared" si="5"/>
+      <c r="I43" s="25">
+        <f t="shared" si="9"/>
         <v>1475</v>
       </c>
-      <c r="J43" s="28">
-        <f t="shared" si="5"/>
+      <c r="J43" s="23">
+        <f t="shared" si="9"/>
         <v>541</v>
       </c>
-      <c r="K43" s="28">
-        <f t="shared" si="5"/>
+      <c r="K43" s="23">
+        <f t="shared" si="9"/>
         <v>780</v>
       </c>
-      <c r="L43" s="28">
-        <f t="shared" si="5"/>
+      <c r="L43" s="23">
+        <f t="shared" si="9"/>
         <v>107</v>
       </c>
-      <c r="M43" s="28">
-        <f t="shared" si="5"/>
+      <c r="M43" s="23">
+        <f t="shared" si="9"/>
         <v>325</v>
       </c>
-      <c r="N43" s="28">
-        <f t="shared" si="5"/>
+      <c r="N43" s="23">
+        <f t="shared" si="9"/>
         <v>2000</v>
       </c>
-      <c r="O43" s="28">
-        <f t="shared" si="5"/>
+      <c r="O43" s="23">
+        <f t="shared" si="9"/>
         <v>2000</v>
       </c>
-      <c r="P43" s="28">
-        <f t="shared" si="5"/>
+      <c r="P43" s="23">
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="Q43" s="28">
-        <f t="shared" si="5"/>
+      <c r="Q43" s="23">
+        <f t="shared" si="9"/>
         <v>210</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A44" s="40" t="s">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" s="50" t="s">
         <v>25</v>
       </c>
       <c r="B44" s="12">
         <v>45962</v>
       </c>
-      <c r="C44" s="26">
-        <v>30</v>
+      <c r="C44" s="21">
+        <v>138</v>
       </c>
       <c r="D44" s="5">
         <v>160</v>
@@ -6745,11 +6686,11 @@
       <c r="G44" s="5">
         <v>87</v>
       </c>
-      <c r="H44" s="23">
+      <c r="H44" s="20">
         <f>540+250+165</f>
         <v>955</v>
       </c>
-      <c r="I44" s="24">
+      <c r="I44" s="21">
         <v>240</v>
       </c>
       <c r="J44" s="5">
@@ -6765,10 +6706,10 @@
         <f>27+34</f>
         <v>61</v>
       </c>
-      <c r="N44" s="52">
+      <c r="N44" s="65">
         <v>2000</v>
       </c>
-      <c r="O44" s="52">
+      <c r="O44" s="65">
         <v>2000</v>
       </c>
       <c r="P44" s="5">
@@ -6778,13 +6719,13 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A45" s="40"/>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A45" s="50"/>
       <c r="B45" s="12">
         <v>45992</v>
       </c>
-      <c r="C45" s="15">
-        <v>102</v>
+      <c r="C45" s="16">
+        <v>189</v>
       </c>
       <c r="D45" s="6">
         <v>211</v>
@@ -6798,10 +6739,10 @@
       <c r="G45" s="6">
         <v>5</v>
       </c>
-      <c r="H45" s="16">
+      <c r="H45" s="15">
         <v>100</v>
       </c>
-      <c r="I45" s="17">
+      <c r="I45" s="16">
         <v>320</v>
       </c>
       <c r="J45" s="6">
@@ -6816,8 +6757,8 @@
       <c r="M45" s="6">
         <v>2</v>
       </c>
-      <c r="N45" s="53"/>
-      <c r="O45" s="53"/>
+      <c r="N45" s="66"/>
+      <c r="O45" s="66"/>
       <c r="P45" s="6">
         <v>2</v>
       </c>
@@ -6825,13 +6766,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A46" s="40"/>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A46" s="50"/>
       <c r="B46" s="12">
         <v>46023</v>
       </c>
-      <c r="C46" s="15">
-        <v>58</v>
+      <c r="C46" s="16">
+        <v>358</v>
       </c>
       <c r="D46" s="6">
         <v>347</v>
@@ -6845,10 +6786,10 @@
       <c r="G46" s="6">
         <v>0</v>
       </c>
-      <c r="H46" s="16">
-        <v>0</v>
-      </c>
-      <c r="I46" s="17">
+      <c r="H46" s="15">
+        <v>0</v>
+      </c>
+      <c r="I46" s="16">
         <v>160</v>
       </c>
       <c r="J46" s="6">
@@ -6863,8 +6804,8 @@
       <c r="M46" s="6">
         <v>0</v>
       </c>
-      <c r="N46" s="53"/>
-      <c r="O46" s="53"/>
+      <c r="N46" s="66"/>
+      <c r="O46" s="66"/>
       <c r="P46" s="6">
         <v>1</v>
       </c>
@@ -6872,13 +6813,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A47" s="40"/>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" s="50"/>
       <c r="B47" s="12">
         <v>46054</v>
       </c>
-      <c r="C47" s="15">
-        <v>65</v>
+      <c r="C47" s="16">
+        <v>365</v>
       </c>
       <c r="D47" s="6">
         <v>412</v>
@@ -6892,10 +6833,10 @@
       <c r="G47" s="6">
         <v>16</v>
       </c>
-      <c r="H47" s="16">
+      <c r="H47" s="15">
         <v>555</v>
       </c>
-      <c r="I47" s="17">
+      <c r="I47" s="16">
         <v>100</v>
       </c>
       <c r="J47" s="6">
@@ -6911,8 +6852,8 @@
         <f>21+13</f>
         <v>34</v>
       </c>
-      <c r="N47" s="53"/>
-      <c r="O47" s="53"/>
+      <c r="N47" s="66"/>
+      <c r="O47" s="66"/>
       <c r="P47" s="6">
         <v>1</v>
       </c>
@@ -6920,12 +6861,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A48" s="40"/>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A48" s="50"/>
       <c r="B48" s="12">
         <v>46082</v>
       </c>
-      <c r="C48" s="15">
+      <c r="C48" s="16">
         <v>70</v>
       </c>
       <c r="D48" s="6">
@@ -6940,10 +6881,10 @@
       <c r="G48" s="6">
         <v>0</v>
       </c>
-      <c r="H48" s="16">
-        <v>0</v>
-      </c>
-      <c r="I48" s="31">
+      <c r="H48" s="15">
+        <v>0</v>
+      </c>
+      <c r="I48" s="26">
         <v>130</v>
       </c>
       <c r="J48" s="6">
@@ -6958,8 +6899,8 @@
       <c r="M48" s="6">
         <v>0</v>
       </c>
-      <c r="N48" s="53"/>
-      <c r="O48" s="53"/>
+      <c r="N48" s="66"/>
+      <c r="O48" s="66"/>
       <c r="P48" s="6">
         <v>0</v>
       </c>
@@ -6967,12 +6908,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A49" s="40"/>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A49" s="50"/>
       <c r="B49" s="12">
         <v>46113</v>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="16">
         <v>52</v>
       </c>
       <c r="D49" s="6">
@@ -6987,10 +6928,10 @@
       <c r="G49" s="6">
         <v>0</v>
       </c>
-      <c r="H49" s="16">
+      <c r="H49" s="15">
         <v>200</v>
       </c>
-      <c r="I49" s="31">
+      <c r="I49" s="26">
         <v>140</v>
       </c>
       <c r="J49" s="6">
@@ -7005,8 +6946,8 @@
       <c r="M49" s="6">
         <v>38</v>
       </c>
-      <c r="N49" s="53"/>
-      <c r="O49" s="53"/>
+      <c r="N49" s="66"/>
+      <c r="O49" s="66"/>
       <c r="P49" s="6">
         <v>0</v>
       </c>
@@ -7014,13 +6955,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A50" s="40"/>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A50" s="50"/>
       <c r="B50" s="12">
         <v>46143</v>
       </c>
-      <c r="C50" s="15">
-        <v>48</v>
+      <c r="C50" s="16">
+        <v>188</v>
       </c>
       <c r="D50" s="6">
         <v>285</v>
@@ -7034,10 +6975,10 @@
       <c r="G50" s="6">
         <v>13</v>
       </c>
-      <c r="H50" s="16">
+      <c r="H50" s="15">
         <v>210</v>
       </c>
-      <c r="I50" s="31">
+      <c r="I50" s="26">
         <v>180</v>
       </c>
       <c r="J50" s="6">
@@ -7052,8 +6993,8 @@
       <c r="M50" s="6">
         <v>29</v>
       </c>
-      <c r="N50" s="53"/>
-      <c r="O50" s="53"/>
+      <c r="N50" s="66"/>
+      <c r="O50" s="66"/>
       <c r="P50" s="6">
         <v>2</v>
       </c>
@@ -7061,13 +7002,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A51" s="40"/>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A51" s="50"/>
       <c r="B51" s="12">
         <v>46174</v>
       </c>
-      <c r="C51" s="15">
-        <v>20</v>
+      <c r="C51" s="16">
+        <v>259</v>
       </c>
       <c r="D51" s="6">
         <v>393</v>
@@ -7081,10 +7022,10 @@
       <c r="G51" s="6">
         <v>0</v>
       </c>
-      <c r="H51" s="16">
-        <v>0</v>
-      </c>
-      <c r="I51" s="31">
+      <c r="H51" s="15">
+        <v>0</v>
+      </c>
+      <c r="I51" s="26">
         <v>160</v>
       </c>
       <c r="J51" s="6">
@@ -7099,8 +7040,8 @@
       <c r="M51" s="6">
         <v>0</v>
       </c>
-      <c r="N51" s="53"/>
-      <c r="O51" s="53"/>
+      <c r="N51" s="66"/>
+      <c r="O51" s="66"/>
       <c r="P51" s="6">
         <v>1</v>
       </c>
@@ -7108,13 +7049,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="40"/>
+    <row r="52" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="50"/>
       <c r="B52" s="10">
         <v>46204</v>
       </c>
-      <c r="C52" s="18">
-        <v>30</v>
+      <c r="C52" s="39">
+        <v>203</v>
       </c>
       <c r="D52" s="7">
         <v>233</v>
@@ -7128,13 +7069,13 @@
       <c r="G52" s="7">
         <v>12</v>
       </c>
-      <c r="H52" s="19">
+      <c r="H52" s="17">
         <v>150</v>
       </c>
-      <c r="I52" s="32">
+      <c r="I52" s="27">
         <v>180</v>
       </c>
-      <c r="J52" s="20">
+      <c r="J52" s="18">
         <v>90</v>
       </c>
       <c r="K52" s="7">
@@ -7146,8 +7087,8 @@
       <c r="M52" s="7">
         <v>0</v>
       </c>
-      <c r="N52" s="54"/>
-      <c r="O52" s="54"/>
+      <c r="N52" s="67"/>
+      <c r="O52" s="67"/>
       <c r="P52" s="7">
         <v>1</v>
       </c>
@@ -7155,140 +7096,152 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="65" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="40"/>
-      <c r="B53" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="C53" s="27">
-        <f t="shared" ref="C53:Q53" si="6">+C44+C45+C46+C47+C48+C49+C50+C51+C52</f>
-        <v>475</v>
-      </c>
-      <c r="D53" s="28">
-        <f t="shared" si="6"/>
+    <row r="53" spans="1:17" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="50"/>
+      <c r="B53" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="25">
+        <f t="shared" ref="C53" si="10">+C44+C45+C46+C47+C48+C49+C50+C51+C52</f>
+        <v>1822</v>
+      </c>
+      <c r="D53" s="23">
+        <f t="shared" ref="D53:Q53" si="11">+D44+D45+D46+D47+D48+D49+D50+D51+D52</f>
         <v>2236</v>
       </c>
-      <c r="E53" s="28">
-        <f t="shared" si="6"/>
+      <c r="E53" s="23">
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
-      <c r="F53" s="28">
-        <f t="shared" si="6"/>
+      <c r="F53" s="23">
+        <f t="shared" si="11"/>
         <v>169</v>
       </c>
-      <c r="G53" s="28">
-        <f t="shared" si="6"/>
+      <c r="G53" s="23">
+        <f t="shared" si="11"/>
         <v>133</v>
       </c>
-      <c r="H53" s="29">
-        <f t="shared" si="6"/>
+      <c r="H53" s="24">
+        <f t="shared" si="11"/>
         <v>2170</v>
       </c>
-      <c r="I53" s="30">
-        <f t="shared" si="6"/>
+      <c r="I53" s="25">
+        <f t="shared" si="11"/>
         <v>1610</v>
       </c>
-      <c r="J53" s="30">
-        <f t="shared" si="6"/>
+      <c r="J53" s="25">
+        <f t="shared" si="11"/>
         <v>740</v>
       </c>
-      <c r="K53" s="28">
-        <f t="shared" si="6"/>
+      <c r="K53" s="23">
+        <f t="shared" si="11"/>
         <v>885</v>
       </c>
-      <c r="L53" s="28">
-        <f t="shared" si="6"/>
+      <c r="L53" s="23">
+        <f t="shared" si="11"/>
         <v>45</v>
       </c>
-      <c r="M53" s="28">
-        <f t="shared" si="6"/>
+      <c r="M53" s="23">
+        <f t="shared" si="11"/>
         <v>164</v>
       </c>
-      <c r="N53" s="28">
-        <f t="shared" si="6"/>
+      <c r="N53" s="23">
+        <f t="shared" si="11"/>
         <v>2000</v>
       </c>
-      <c r="O53" s="28">
-        <f t="shared" si="6"/>
+      <c r="O53" s="23">
+        <f t="shared" si="11"/>
         <v>2000</v>
       </c>
-      <c r="P53" s="28">
-        <f t="shared" si="6"/>
+      <c r="P53" s="23">
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
-      <c r="Q53" s="28">
-        <f t="shared" si="6"/>
+      <c r="Q53" s="23">
+        <f t="shared" si="11"/>
         <v>189</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="81" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="55" t="s">
+    <row r="54" spans="1:17" s="49" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="B54" s="56"/>
-      <c r="C54" s="78">
-        <f t="shared" ref="C54:Q54" si="7">+C53+C43+C33+C23+C13</f>
-        <v>2813</v>
-      </c>
-      <c r="D54" s="79">
-        <f t="shared" si="7"/>
+      <c r="B54" s="69"/>
+      <c r="C54" s="46">
+        <f t="shared" ref="C54:Q54" si="12">+C53+C43+C33+C23+C13</f>
+        <v>7140</v>
+      </c>
+      <c r="D54" s="47">
+        <f t="shared" si="12"/>
         <v>10489</v>
       </c>
-      <c r="E54" s="79">
-        <f t="shared" si="7"/>
+      <c r="E54" s="47">
+        <f t="shared" si="12"/>
         <v>226</v>
       </c>
-      <c r="F54" s="79">
-        <f t="shared" si="7"/>
+      <c r="F54" s="47">
+        <f t="shared" si="12"/>
         <v>1199</v>
       </c>
-      <c r="G54" s="79">
-        <f t="shared" si="7"/>
+      <c r="G54" s="47">
+        <f t="shared" si="12"/>
         <v>1258</v>
       </c>
-      <c r="H54" s="80">
-        <f t="shared" si="7"/>
+      <c r="H54" s="48">
+        <f t="shared" si="12"/>
         <v>14164</v>
       </c>
-      <c r="I54" s="79">
-        <f t="shared" si="7"/>
+      <c r="I54" s="47">
+        <f t="shared" si="12"/>
         <v>7005</v>
       </c>
-      <c r="J54" s="79">
-        <f t="shared" si="7"/>
-        <v>2925</v>
-      </c>
-      <c r="K54" s="79">
-        <f t="shared" si="7"/>
+      <c r="J54" s="47">
+        <f t="shared" si="12"/>
+        <v>3120</v>
+      </c>
+      <c r="K54" s="47">
+        <f t="shared" si="12"/>
         <v>3331</v>
       </c>
-      <c r="L54" s="79">
-        <f t="shared" si="7"/>
+      <c r="L54" s="47">
+        <f t="shared" si="12"/>
         <v>247</v>
       </c>
-      <c r="M54" s="79">
-        <f t="shared" si="7"/>
+      <c r="M54" s="47">
+        <f t="shared" si="12"/>
         <v>904</v>
       </c>
-      <c r="N54" s="79">
-        <f t="shared" si="7"/>
+      <c r="N54" s="47">
+        <f t="shared" si="12"/>
         <v>12000</v>
       </c>
-      <c r="O54" s="79">
-        <f t="shared" si="7"/>
+      <c r="O54" s="47">
+        <f t="shared" si="12"/>
         <v>10000</v>
       </c>
-      <c r="P54" s="79">
-        <f t="shared" si="7"/>
+      <c r="P54" s="47">
+        <f t="shared" si="12"/>
         <v>134</v>
       </c>
-      <c r="Q54" s="79">
-        <f t="shared" si="7"/>
+      <c r="Q54" s="47">
+        <f t="shared" si="12"/>
         <v>972</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A4:A13"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="J2:Q2"/>
+    <mergeCell ref="N4:N12"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A44:A53"/>
+    <mergeCell ref="A34:A43"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A14:A23"/>
     <mergeCell ref="N14:N22"/>
     <mergeCell ref="N24:N32"/>
     <mergeCell ref="N34:N42"/>
@@ -7298,18 +7251,6 @@
     <mergeCell ref="O24:O32"/>
     <mergeCell ref="O34:O42"/>
     <mergeCell ref="O44:O52"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A44:A53"/>
-    <mergeCell ref="A34:A43"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A14:A23"/>
-    <mergeCell ref="A4:A13"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="J2:Q2"/>
-    <mergeCell ref="N4:N12"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
